--- a/src/scrapper/database/dbs/files_csv/database_export.xlsx
+++ b/src/scrapper/database/dbs/files_csv/database_export.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="faculty" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="course" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="course_unit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="course_metadata" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="info" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="course_group" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="course_unit_course_group" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="faculty" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="course" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="course_unit" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="course_metadata" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="course_group" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="course_unit_course_group" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="students_in_course_units" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Student Overlap" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,13 +33,27 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,8 +68,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +479,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-22 08:41:17.828143</t>
+          <t>2026-05-27 00:04:50.140695</t>
         </is>
       </c>
     </row>
@@ -557,7 +583,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:00.486211</t>
+          <t>2026-05-27 00:05:58.456767</t>
         </is>
       </c>
     </row>
@@ -600,7 +626,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-22 08:46:00.810542</t>
+          <t>2026-05-27 00:07:05.338492</t>
         </is>
       </c>
     </row>
@@ -643,7 +669,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:16.302330</t>
+          <t>2026-05-27 00:06:41.857662</t>
         </is>
       </c>
     </row>
@@ -686,7 +712,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:37.108188</t>
+          <t>2026-05-27 00:06:51.387715</t>
         </is>
       </c>
     </row>
@@ -729,7 +755,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:24.372722</t>
+          <t>2026-05-27 00:06:48.262232</t>
         </is>
       </c>
     </row>
@@ -772,7 +798,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-22 08:46:21.911857</t>
+          <t>2026-05-27 00:07:13.253627</t>
         </is>
       </c>
     </row>
@@ -815,7 +841,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-22 08:46:00.189434</t>
+          <t>2026-05-27 00:07:02.594701</t>
         </is>
       </c>
     </row>
@@ -858,7 +884,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:51.556476</t>
+          <t>2026-05-27 00:06:59.867020</t>
         </is>
       </c>
     </row>
@@ -901,7 +927,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-22 08:46:11.984867</t>
+          <t>2026-05-27 00:07:11.125517</t>
         </is>
       </c>
     </row>
@@ -944,7 +970,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-05-22 08:46:11.541465</t>
+          <t>2026-05-27 00:07:08.280126</t>
         </is>
       </c>
     </row>
@@ -987,7 +1013,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:01.673152</t>
+          <t>2026-05-27 00:06:32.541194</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1056,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:19.513328</t>
+          <t>2026-05-27 00:06:44.368786</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1099,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:43.114531</t>
+          <t>2026-05-27 00:06:54.158261</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1142,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:24.113193</t>
+          <t>2026-05-27 00:06:46.352006</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1185,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:37.415578</t>
+          <t>2026-05-27 00:06:52.728864</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1228,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-05-22 08:42:25.251833</t>
+          <t>2026-05-27 00:05:17.991671</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1271,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-05-22 08:42:51.347554</t>
+          <t>2026-05-27 00:05:34.908560</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1314,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-05-22 08:42:22.827832</t>
+          <t>2026-05-27 00:05:15.912765</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1357,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-05-22 08:42:26.754958</t>
+          <t>2026-05-27 00:05:20.892977</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1400,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-05-22 08:42:51.978538</t>
+          <t>2026-05-27 00:05:36.682034</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1443,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-05-22 08:41:28.261959</t>
+          <t>2026-05-27 00:04:59.038275</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1486,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-05-22 08:42:28.637581</t>
+          <t>2026-05-27 00:05:23.371751</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1529,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:05.898714</t>
+          <t>2026-05-27 00:06:34.393500</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1572,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:15.978850</t>
+          <t>2026-05-27 00:06:39.575679</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1615,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-05-22 08:43:50.768721</t>
+          <t>2026-05-27 00:05:51.092396</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1658,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:51.214739</t>
+          <t>2026-05-27 00:06:56.973612</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1701,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:55.060167</t>
+          <t>2026-05-27 00:05:09.190531</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1744,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:06.251552</t>
+          <t>2026-05-27 00:06:37.352693</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1787,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-05-22 08:45:01.140038</t>
+          <t>2026-05-27 00:06:29.863609</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1830,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:54.691295</t>
+          <t>2026-05-27 00:05:14.073506</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1873,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-05-22 08:42:11.928141</t>
+          <t>2026-05-27 00:05:11.305366</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1916,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-05-22 08:43:54.523170</t>
+          <t>2026-05-27 00:05:52.933590</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1959,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-05-22 08:42:38.830952</t>
+          <t>2026-05-27 00:05:32.146954</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2002,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-05-22 08:41:31.296428</t>
+          <t>2026-05-27 00:05:01.934987</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2045,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-05-22 08:43:41.784186</t>
+          <t>2026-05-27 00:05:47.468344</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2088,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-05-22 08:43:42.553903</t>
+          <t>2026-05-27 00:05:49.784702</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2131,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-05-22 08:41:39.651854</t>
+          <t>2026-05-27 00:05:07.197616</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2174,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:43.756336</t>
+          <t>2026-05-27 00:06:25.332207</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2217,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:35.156424</t>
+          <t>2026-05-27 00:06:21.565663</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2260,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:31.737016</t>
+          <t>2026-05-27 00:06:16.957939</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2303,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-05-22 08:43:31.540345</t>
+          <t>2026-05-27 00:05:43.307616</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2346,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-05-22 08:43:33.046646</t>
+          <t>2026-05-27 00:05:45.224030</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2389,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:08.740051</t>
+          <t>2026-05-27 00:06:00.433903</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2432,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-05-22 08:43:55.837764</t>
+          <t>2026-05-27 00:05:54.759450</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2475,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:32.080485</t>
+          <t>2026-05-27 00:06:19.656546</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2518,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:20.966594</t>
+          <t>2026-05-27 00:06:11.706432</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2561,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-05-22 08:43:06.707448</t>
+          <t>2026-05-27 00:05:38.652192</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2604,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:24.199690</t>
+          <t>2026-05-27 00:06:14.574923</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2647,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-05-22 08:42:33.566382</t>
+          <t>2026-05-27 00:05:28.782224</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2690,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-05-22 08:43:26.697674</t>
+          <t>2026-05-27 00:05:41.255353</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2733,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:15.210191</t>
+          <t>2026-05-27 00:06:05.835444</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2776,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:00.204244</t>
+          <t>2026-05-27 00:05:56.613223</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2819,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-05-22 08:42:31.139773</t>
+          <t>2026-05-27 00:05:26.381098</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2862,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:20.625717</t>
+          <t>2026-05-27 00:06:08.851398</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2905,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:43.378591</t>
+          <t>2026-05-27 00:06:22.781127</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2948,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-05-22 08:42:37.489591</t>
+          <t>2026-05-27 00:05:30.900112</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2991,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:46.677007</t>
+          <t>2026-05-27 00:06:28.190661</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3034,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-05-22 08:41:39.286858</t>
+          <t>2026-05-27 00:05:04.685371</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3077,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-05-22 08:44:09.065908</t>
+          <t>2026-05-27 00:06:03.381934</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3177,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-22 08:46:45.864842</t>
+          <t>2026-05-27 00:07:28.115406</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3211,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-22 08:47:58.723599</t>
+          <t>2026-05-27 00:07:35.254580</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3245,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-22 08:48:04.023617</t>
+          <t>2026-05-27 00:07:40.246313</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3279,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-22 08:46:37.206636</t>
+          <t>2026-05-27 00:07:22.767520</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3313,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-05-22 08:47:55.414293</t>
+          <t>2026-05-27 00:07:30.418590</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3347,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-22 08:48:11.748002</t>
+          <t>2026-05-27 00:07:46.946601</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3381,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-22 08:48:06.100102</t>
+          <t>2026-05-27 00:07:42.187682</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3415,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-05-22 08:48:15.743570</t>
+          <t>2026-05-27 00:07:51.961089</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3449,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-22 08:48:17.989004</t>
+          <t>2026-05-27 00:07:54.732441</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3483,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-05-22 08:48:15.458897</t>
+          <t>2026-05-27 00:07:49.650637</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3517,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-05-22 08:48:09.536512</t>
+          <t>2026-05-27 00:07:43.983589</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3551,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-05-22 08:48:20.483899</t>
+          <t>2026-05-27 00:07:57.627788</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3585,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-05-22 08:46:44.523442</t>
+          <t>2026-05-27 00:07:25.466548</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3619,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-05-22 08:48:01.520055</t>
+          <t>2026-05-27 00:07:38.175159</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3653,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-05-22 08:47:55.963756</t>
+          <t>2026-05-27 00:07:32.286336</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3666,27 +3692,19 @@
           <t>ects</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>student_count</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>10861</v>
       </c>
       <c r="B2" t="n">
-        <v>559728</v>
+        <v>559654</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -3694,16 +3712,13 @@
         <v>10861</v>
       </c>
       <c r="B3" t="n">
-        <v>559727</v>
+        <v>559728</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
-      </c>
-      <c r="E3" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -3711,16 +3726,13 @@
         <v>10861</v>
       </c>
       <c r="B4" t="n">
-        <v>559726</v>
+        <v>559727</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
-      </c>
-      <c r="E4" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -3728,16 +3740,13 @@
         <v>10861</v>
       </c>
       <c r="B5" t="n">
-        <v>559725</v>
+        <v>559726</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
-      </c>
-      <c r="E5" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -3745,16 +3754,13 @@
         <v>10861</v>
       </c>
       <c r="B6" t="n">
-        <v>559664</v>
+        <v>559725</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -3762,16 +3768,13 @@
         <v>10861</v>
       </c>
       <c r="B7" t="n">
-        <v>559663</v>
+        <v>559664</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
-      </c>
-      <c r="E7" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -3779,16 +3782,13 @@
         <v>10861</v>
       </c>
       <c r="B8" t="n">
-        <v>559662</v>
+        <v>559663</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
-      </c>
-      <c r="E8" t="n">
-        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -3796,16 +3796,13 @@
         <v>10861</v>
       </c>
       <c r="B9" t="n">
-        <v>559661</v>
+        <v>559662</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -3813,16 +3810,13 @@
         <v>10861</v>
       </c>
       <c r="B10" t="n">
-        <v>559660</v>
+        <v>559661</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -3830,16 +3824,13 @@
         <v>10861</v>
       </c>
       <c r="B11" t="n">
-        <v>559659</v>
+        <v>559660</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
-      </c>
-      <c r="E11" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -3847,16 +3838,13 @@
         <v>10861</v>
       </c>
       <c r="B12" t="n">
-        <v>559658</v>
+        <v>559659</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -3864,16 +3852,13 @@
         <v>10861</v>
       </c>
       <c r="B13" t="n">
-        <v>559657</v>
+        <v>559658</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
-      </c>
-      <c r="E13" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -3881,16 +3866,13 @@
         <v>10861</v>
       </c>
       <c r="B14" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
-      </c>
-      <c r="E14" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -3898,16 +3880,13 @@
         <v>10861</v>
       </c>
       <c r="B15" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -3915,16 +3894,13 @@
         <v>10861</v>
       </c>
       <c r="B16" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3951,7 +3927,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 08:41:10.104823</t>
+          <t>2026-05-27 00:04:42.259642</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3994,44 +3970,6 @@
         <is>
           <t>semester</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>36744721</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Unidades Curriculares Optativas - 2º Grupo</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>10861</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>36746612</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Unidades Curriculares Optativas - 1º Grupo</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>10861</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4045,7 +3983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4060,36 +3998,5636 @@
         </is>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B590"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>student_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>course_unit_id</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>559727</v>
+        <v>202502507</v>
       </c>
       <c r="B2" t="n">
-        <v>36744721</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>559728</v>
+        <v>202500539</v>
       </c>
       <c r="B3" t="n">
-        <v>36744721</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>559663</v>
+        <v>202208028</v>
       </c>
       <c r="B4" t="n">
-        <v>36746612</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>202108685</v>
+      </c>
+      <c r="B5" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>202100684</v>
+      </c>
+      <c r="B6" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>202109775</v>
+      </c>
+      <c r="B7" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>202510620</v>
+      </c>
+      <c r="B8" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>202503496</v>
+      </c>
+      <c r="B9" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>202206097</v>
+      </c>
+      <c r="B10" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>202510621</v>
+      </c>
+      <c r="B11" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>200907258</v>
+      </c>
+      <c r="B12" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>202107100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>202206173</v>
+      </c>
+      <c r="B14" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>202500541</v>
+      </c>
+      <c r="B15" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>202500542</v>
+      </c>
+      <c r="B16" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>202205629</v>
+      </c>
+      <c r="B17" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>202210537</v>
+      </c>
+      <c r="B18" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>202510622</v>
+      </c>
+      <c r="B19" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>202502508</v>
+      </c>
+      <c r="B20" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>202502841</v>
+      </c>
+      <c r="B21" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>202102359</v>
+      </c>
+      <c r="B22" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>202500543</v>
+      </c>
+      <c r="B23" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>202511053</v>
+      </c>
+      <c r="B24" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>202503416</v>
+      </c>
+      <c r="B25" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>202206636</v>
+      </c>
+      <c r="B26" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>202007851</v>
+      </c>
+      <c r="B27" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>202205318</v>
+      </c>
+      <c r="B28" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>202500544</v>
+      </c>
+      <c r="B29" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>202502510</v>
+      </c>
+      <c r="B30" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>202205022</v>
+      </c>
+      <c r="B31" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>202204883</v>
+      </c>
+      <c r="B32" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>202108673</v>
+      </c>
+      <c r="B33" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>202207871</v>
+      </c>
+      <c r="B34" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>202508437</v>
+      </c>
+      <c r="B35" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>202208726</v>
+      </c>
+      <c r="B36" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>202511257</v>
+      </c>
+      <c r="B37" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>202108877</v>
+      </c>
+      <c r="B38" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>202500545</v>
+      </c>
+      <c r="B39" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>202204802</v>
+      </c>
+      <c r="B40" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>202211070</v>
+      </c>
+      <c r="B41" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>201606434</v>
+      </c>
+      <c r="B42" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>202008219</v>
+      </c>
+      <c r="B43" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>202501687</v>
+      </c>
+      <c r="B44" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>202502849</v>
+      </c>
+      <c r="B45" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>202510623</v>
+      </c>
+      <c r="B46" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>202206180</v>
+      </c>
+      <c r="B47" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>202502654</v>
+      </c>
+      <c r="B48" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>202208957</v>
+      </c>
+      <c r="B49" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>202510624</v>
+      </c>
+      <c r="B50" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>202108751</v>
+      </c>
+      <c r="B51" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>202500548</v>
+      </c>
+      <c r="B52" t="n">
+        <v>559657</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>202108860</v>
+      </c>
+      <c r="B53" t="n">
+        <v>559728</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>202400068</v>
+      </c>
+      <c r="B54" t="n">
+        <v>559728</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>201908253</v>
+      </c>
+      <c r="B55" t="n">
+        <v>559728</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>202108879</v>
+      </c>
+      <c r="B56" t="n">
+        <v>559728</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>202108683</v>
+      </c>
+      <c r="B57" t="n">
+        <v>559728</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>202502849</v>
+      </c>
+      <c r="B58" t="n">
+        <v>559728</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>202108809</v>
+      </c>
+      <c r="B59" t="n">
+        <v>559728</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>201906293</v>
+      </c>
+      <c r="B60" t="n">
+        <v>559728</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>202502654</v>
+      </c>
+      <c r="B61" t="n">
+        <v>559728</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>202403111</v>
+      </c>
+      <c r="B62" t="n">
+        <v>559728</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>202400071</v>
+      </c>
+      <c r="B63" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>202109244</v>
+      </c>
+      <c r="B64" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>201902431</v>
+      </c>
+      <c r="B65" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>202508617</v>
+      </c>
+      <c r="B66" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>202108693</v>
+      </c>
+      <c r="B67" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>202108767</v>
+      </c>
+      <c r="B68" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>202308712</v>
+      </c>
+      <c r="B69" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>202108712</v>
+      </c>
+      <c r="B70" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>202402636</v>
+      </c>
+      <c r="B71" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>201902398</v>
+      </c>
+      <c r="B72" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>202503094</v>
+      </c>
+      <c r="B73" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>202004453</v>
+      </c>
+      <c r="B74" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>202008219</v>
+      </c>
+      <c r="B75" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>201304504</v>
+      </c>
+      <c r="B76" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>202502849</v>
+      </c>
+      <c r="B77" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>202108853</v>
+      </c>
+      <c r="B78" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>202401669</v>
+      </c>
+      <c r="B79" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>202409903</v>
+      </c>
+      <c r="B80" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>202403077</v>
+      </c>
+      <c r="B81" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>202108653</v>
+      </c>
+      <c r="B82" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>202502654</v>
+      </c>
+      <c r="B83" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>202108708</v>
+      </c>
+      <c r="B84" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>202108807</v>
+      </c>
+      <c r="B85" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>202103631</v>
+      </c>
+      <c r="B86" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>202108681</v>
+      </c>
+      <c r="B87" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>202108840</v>
+      </c>
+      <c r="B88" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>202502844</v>
+      </c>
+      <c r="B89" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>202508615</v>
+      </c>
+      <c r="B90" t="n">
+        <v>559727</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>202400040</v>
+      </c>
+      <c r="B91" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>202400071</v>
+      </c>
+      <c r="B92" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>202108860</v>
+      </c>
+      <c r="B93" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>202400068</v>
+      </c>
+      <c r="B94" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>202107100</v>
+      </c>
+      <c r="B95" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>202400037</v>
+      </c>
+      <c r="B96" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>201908253</v>
+      </c>
+      <c r="B97" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>202108693</v>
+      </c>
+      <c r="B98" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>202108767</v>
+      </c>
+      <c r="B99" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>202308712</v>
+      </c>
+      <c r="B100" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>202108737</v>
+      </c>
+      <c r="B101" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>202108848</v>
+      </c>
+      <c r="B102" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>202108879</v>
+      </c>
+      <c r="B103" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>202108712</v>
+      </c>
+      <c r="B104" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>202402636</v>
+      </c>
+      <c r="B105" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>202302527</v>
+      </c>
+      <c r="B106" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>201902398</v>
+      </c>
+      <c r="B107" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>202108683</v>
+      </c>
+      <c r="B108" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>202004453</v>
+      </c>
+      <c r="B109" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>202008219</v>
+      </c>
+      <c r="B110" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>201304504</v>
+      </c>
+      <c r="B111" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>202108853</v>
+      </c>
+      <c r="B112" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>202401669</v>
+      </c>
+      <c r="B113" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>202409903</v>
+      </c>
+      <c r="B114" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>202108809</v>
+      </c>
+      <c r="B115" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>202403077</v>
+      </c>
+      <c r="B116" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>202108653</v>
+      </c>
+      <c r="B117" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>202108756</v>
+      </c>
+      <c r="B118" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>201906293</v>
+      </c>
+      <c r="B119" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>202103337</v>
+      </c>
+      <c r="B120" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>202108708</v>
+      </c>
+      <c r="B121" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>202108807</v>
+      </c>
+      <c r="B122" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>202103631</v>
+      </c>
+      <c r="B123" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>202302522</v>
+      </c>
+      <c r="B124" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>202108681</v>
+      </c>
+      <c r="B125" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>202403111</v>
+      </c>
+      <c r="B126" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>202108840</v>
+      </c>
+      <c r="B127" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>202400393</v>
+      </c>
+      <c r="B128" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>202402696</v>
+      </c>
+      <c r="B129" t="n">
+        <v>559726</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>202400040</v>
+      </c>
+      <c r="B130" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>202400071</v>
+      </c>
+      <c r="B131" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>202108860</v>
+      </c>
+      <c r="B132" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>202108745</v>
+      </c>
+      <c r="B133" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>202400068</v>
+      </c>
+      <c r="B134" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>202107100</v>
+      </c>
+      <c r="B135" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>202400037</v>
+      </c>
+      <c r="B136" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>202108693</v>
+      </c>
+      <c r="B137" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>202108767</v>
+      </c>
+      <c r="B138" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>202308712</v>
+      </c>
+      <c r="B139" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>202108737</v>
+      </c>
+      <c r="B140" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>202108848</v>
+      </c>
+      <c r="B141" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>202108879</v>
+      </c>
+      <c r="B142" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>202108712</v>
+      </c>
+      <c r="B143" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>202402636</v>
+      </c>
+      <c r="B144" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>202302527</v>
+      </c>
+      <c r="B145" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>201902398</v>
+      </c>
+      <c r="B146" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>202108683</v>
+      </c>
+      <c r="B147" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>202004453</v>
+      </c>
+      <c r="B148" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>201304504</v>
+      </c>
+      <c r="B149" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>202108853</v>
+      </c>
+      <c r="B150" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>202401669</v>
+      </c>
+      <c r="B151" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>202409903</v>
+      </c>
+      <c r="B152" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>202108809</v>
+      </c>
+      <c r="B153" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>202403077</v>
+      </c>
+      <c r="B154" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>202108653</v>
+      </c>
+      <c r="B155" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>202108756</v>
+      </c>
+      <c r="B156" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>201906293</v>
+      </c>
+      <c r="B157" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>202103337</v>
+      </c>
+      <c r="B158" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>202302862</v>
+      </c>
+      <c r="B159" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>202108708</v>
+      </c>
+      <c r="B160" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>202108807</v>
+      </c>
+      <c r="B161" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>202103631</v>
+      </c>
+      <c r="B162" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>202001957</v>
+      </c>
+      <c r="B163" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>202302522</v>
+      </c>
+      <c r="B164" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>202300431</v>
+      </c>
+      <c r="B165" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>202108681</v>
+      </c>
+      <c r="B166" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>202403111</v>
+      </c>
+      <c r="B167" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>202108840</v>
+      </c>
+      <c r="B168" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>202400393</v>
+      </c>
+      <c r="B169" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>202402696</v>
+      </c>
+      <c r="B170" t="n">
+        <v>559725</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>202108685</v>
+      </c>
+      <c r="B171" t="n">
         <v>559664</v>
       </c>
-      <c r="B5" t="n">
-        <v>36746612</v>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>202511830</v>
+      </c>
+      <c r="B172" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>202206097</v>
+      </c>
+      <c r="B173" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>200907258</v>
+      </c>
+      <c r="B174" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>202109244</v>
+      </c>
+      <c r="B175" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>202500541</v>
+      </c>
+      <c r="B176" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>202500542</v>
+      </c>
+      <c r="B177" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>202205629</v>
+      </c>
+      <c r="B178" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>202510622</v>
+      </c>
+      <c r="B179" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>202511053</v>
+      </c>
+      <c r="B180" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>202503464</v>
+      </c>
+      <c r="B181" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>202205318</v>
+      </c>
+      <c r="B182" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>202502510</v>
+      </c>
+      <c r="B183" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>202108673</v>
+      </c>
+      <c r="B184" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>202511257</v>
+      </c>
+      <c r="B185" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>202108877</v>
+      </c>
+      <c r="B186" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>202409902</v>
+      </c>
+      <c r="B187" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>202204802</v>
+      </c>
+      <c r="B188" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>202510623</v>
+      </c>
+      <c r="B189" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>202401558</v>
+      </c>
+      <c r="B190" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>202409904</v>
+      </c>
+      <c r="B191" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>202500548</v>
+      </c>
+      <c r="B192" t="n">
+        <v>559664</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>202502507</v>
+      </c>
+      <c r="B193" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>202103420</v>
+      </c>
+      <c r="B194" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>202500539</v>
+      </c>
+      <c r="B195" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>202100684</v>
+      </c>
+      <c r="B196" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>202510620</v>
+      </c>
+      <c r="B197" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>202503496</v>
+      </c>
+      <c r="B198" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>202206173</v>
+      </c>
+      <c r="B199" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>202210537</v>
+      </c>
+      <c r="B200" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>202502508</v>
+      </c>
+      <c r="B201" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>202503416</v>
+      </c>
+      <c r="B202" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202206636</v>
+      </c>
+      <c r="B203" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>202511047</v>
+      </c>
+      <c r="B204" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>202205022</v>
+      </c>
+      <c r="B205" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>202204883</v>
+      </c>
+      <c r="B206" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>202207871</v>
+      </c>
+      <c r="B207" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>202208726</v>
+      </c>
+      <c r="B208" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>202500545</v>
+      </c>
+      <c r="B209" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>202514197</v>
+      </c>
+      <c r="B210" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>202502513</v>
+      </c>
+      <c r="B211" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>202206180</v>
+      </c>
+      <c r="B212" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>202208957</v>
+      </c>
+      <c r="B213" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>202512262</v>
+      </c>
+      <c r="B214" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>202108751</v>
+      </c>
+      <c r="B215" t="n">
+        <v>559663</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>202502506</v>
+      </c>
+      <c r="B216" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>202502507</v>
+      </c>
+      <c r="B217" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>202500539</v>
+      </c>
+      <c r="B218" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>202108685</v>
+      </c>
+      <c r="B219" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>202100684</v>
+      </c>
+      <c r="B220" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>202510620</v>
+      </c>
+      <c r="B221" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>202503496</v>
+      </c>
+      <c r="B222" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>202206097</v>
+      </c>
+      <c r="B223" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>202510621</v>
+      </c>
+      <c r="B224" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>200907258</v>
+      </c>
+      <c r="B225" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>202206173</v>
+      </c>
+      <c r="B226" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>202500541</v>
+      </c>
+      <c r="B227" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>202500542</v>
+      </c>
+      <c r="B228" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>202205629</v>
+      </c>
+      <c r="B229" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>202210537</v>
+      </c>
+      <c r="B230" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>202510622</v>
+      </c>
+      <c r="B231" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>202502508</v>
+      </c>
+      <c r="B232" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>202102359</v>
+      </c>
+      <c r="B233" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>202500543</v>
+      </c>
+      <c r="B234" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>202511053</v>
+      </c>
+      <c r="B235" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>202503416</v>
+      </c>
+      <c r="B236" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>202503464</v>
+      </c>
+      <c r="B237" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>202206636</v>
+      </c>
+      <c r="B238" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>202007851</v>
+      </c>
+      <c r="B239" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>202205318</v>
+      </c>
+      <c r="B240" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>202502510</v>
+      </c>
+      <c r="B241" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>202511047</v>
+      </c>
+      <c r="B242" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>202205022</v>
+      </c>
+      <c r="B243" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>202512130</v>
+      </c>
+      <c r="B244" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>202204883</v>
+      </c>
+      <c r="B245" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>202108673</v>
+      </c>
+      <c r="B246" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>202207871</v>
+      </c>
+      <c r="B247" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>202208726</v>
+      </c>
+      <c r="B248" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>202511257</v>
+      </c>
+      <c r="B249" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>202108877</v>
+      </c>
+      <c r="B250" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>202409902</v>
+      </c>
+      <c r="B251" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>202204802</v>
+      </c>
+      <c r="B252" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>202514197</v>
+      </c>
+      <c r="B253" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>202510623</v>
+      </c>
+      <c r="B254" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>202502513</v>
+      </c>
+      <c r="B255" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>202206180</v>
+      </c>
+      <c r="B256" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>202208957</v>
+      </c>
+      <c r="B257" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>202510624</v>
+      </c>
+      <c r="B258" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>202108751</v>
+      </c>
+      <c r="B259" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>202409904</v>
+      </c>
+      <c r="B260" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>202500548</v>
+      </c>
+      <c r="B261" t="n">
+        <v>559662</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>202502506</v>
+      </c>
+      <c r="B262" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>202502507</v>
+      </c>
+      <c r="B263" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>202500539</v>
+      </c>
+      <c r="B264" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>202108685</v>
+      </c>
+      <c r="B265" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>202100684</v>
+      </c>
+      <c r="B266" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>202109775</v>
+      </c>
+      <c r="B267" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>202510620</v>
+      </c>
+      <c r="B268" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>202503496</v>
+      </c>
+      <c r="B269" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>202206097</v>
+      </c>
+      <c r="B270" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>202510621</v>
+      </c>
+      <c r="B271" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>202109244</v>
+      </c>
+      <c r="B272" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>202206173</v>
+      </c>
+      <c r="B273" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>202500541</v>
+      </c>
+      <c r="B274" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>201902431</v>
+      </c>
+      <c r="B275" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>202500542</v>
+      </c>
+      <c r="B276" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>202205629</v>
+      </c>
+      <c r="B277" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>202210537</v>
+      </c>
+      <c r="B278" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>202510622</v>
+      </c>
+      <c r="B279" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>202502508</v>
+      </c>
+      <c r="B280" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>202102359</v>
+      </c>
+      <c r="B281" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>202500543</v>
+      </c>
+      <c r="B282" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>202511053</v>
+      </c>
+      <c r="B283" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>202503416</v>
+      </c>
+      <c r="B284" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>202503464</v>
+      </c>
+      <c r="B285" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>202206636</v>
+      </c>
+      <c r="B286" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>202007851</v>
+      </c>
+      <c r="B287" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>202205318</v>
+      </c>
+      <c r="B288" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>202502510</v>
+      </c>
+      <c r="B289" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>202511047</v>
+      </c>
+      <c r="B290" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>202205022</v>
+      </c>
+      <c r="B291" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>202204883</v>
+      </c>
+      <c r="B292" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>202108673</v>
+      </c>
+      <c r="B293" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>202207871</v>
+      </c>
+      <c r="B294" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>202503094</v>
+      </c>
+      <c r="B295" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>202208726</v>
+      </c>
+      <c r="B296" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>202511257</v>
+      </c>
+      <c r="B297" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>202108877</v>
+      </c>
+      <c r="B298" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>202204802</v>
+      </c>
+      <c r="B299" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>202211070</v>
+      </c>
+      <c r="B300" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>202514197</v>
+      </c>
+      <c r="B301" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>202510623</v>
+      </c>
+      <c r="B302" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>202401558</v>
+      </c>
+      <c r="B303" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>202502513</v>
+      </c>
+      <c r="B304" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>202206180</v>
+      </c>
+      <c r="B305" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>202208957</v>
+      </c>
+      <c r="B306" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>202510624</v>
+      </c>
+      <c r="B307" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>202108751</v>
+      </c>
+      <c r="B308" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>202204180</v>
+      </c>
+      <c r="B309" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>202500548</v>
+      </c>
+      <c r="B310" t="n">
+        <v>559661</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>202502507</v>
+      </c>
+      <c r="B311" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>202500539</v>
+      </c>
+      <c r="B312" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>202108685</v>
+      </c>
+      <c r="B313" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>202100684</v>
+      </c>
+      <c r="B314" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>202109775</v>
+      </c>
+      <c r="B315" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>202510620</v>
+      </c>
+      <c r="B316" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>202503496</v>
+      </c>
+      <c r="B317" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>202206097</v>
+      </c>
+      <c r="B318" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>202510621</v>
+      </c>
+      <c r="B319" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>200907258</v>
+      </c>
+      <c r="B320" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>202206173</v>
+      </c>
+      <c r="B321" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>202500541</v>
+      </c>
+      <c r="B322" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>202500542</v>
+      </c>
+      <c r="B323" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>202205629</v>
+      </c>
+      <c r="B324" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>202210537</v>
+      </c>
+      <c r="B325" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>202510622</v>
+      </c>
+      <c r="B326" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>202502508</v>
+      </c>
+      <c r="B327" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>202102359</v>
+      </c>
+      <c r="B328" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>202500543</v>
+      </c>
+      <c r="B329" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>202511053</v>
+      </c>
+      <c r="B330" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>202503416</v>
+      </c>
+      <c r="B331" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>202503464</v>
+      </c>
+      <c r="B332" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>202206636</v>
+      </c>
+      <c r="B333" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>202007851</v>
+      </c>
+      <c r="B334" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>202205318</v>
+      </c>
+      <c r="B335" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>202502510</v>
+      </c>
+      <c r="B336" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>202511047</v>
+      </c>
+      <c r="B337" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>202205022</v>
+      </c>
+      <c r="B338" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>202512130</v>
+      </c>
+      <c r="B339" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>202204883</v>
+      </c>
+      <c r="B340" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>202108673</v>
+      </c>
+      <c r="B341" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>202207871</v>
+      </c>
+      <c r="B342" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>202208726</v>
+      </c>
+      <c r="B343" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>202511257</v>
+      </c>
+      <c r="B344" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>202108877</v>
+      </c>
+      <c r="B345" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>202204802</v>
+      </c>
+      <c r="B346" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>202211070</v>
+      </c>
+      <c r="B347" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>202514197</v>
+      </c>
+      <c r="B348" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>202510623</v>
+      </c>
+      <c r="B349" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>202502513</v>
+      </c>
+      <c r="B350" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>202206180</v>
+      </c>
+      <c r="B351" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>202208957</v>
+      </c>
+      <c r="B352" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>202512262</v>
+      </c>
+      <c r="B353" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>202510624</v>
+      </c>
+      <c r="B354" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>202108751</v>
+      </c>
+      <c r="B355" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>202500548</v>
+      </c>
+      <c r="B356" t="n">
+        <v>559660</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>202502507</v>
+      </c>
+      <c r="B357" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>202500539</v>
+      </c>
+      <c r="B358" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>202108685</v>
+      </c>
+      <c r="B359" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>202510620</v>
+      </c>
+      <c r="B360" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>202503496</v>
+      </c>
+      <c r="B361" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>202206097</v>
+      </c>
+      <c r="B362" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>202206173</v>
+      </c>
+      <c r="B363" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>202500541</v>
+      </c>
+      <c r="B364" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>202500542</v>
+      </c>
+      <c r="B365" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>202205629</v>
+      </c>
+      <c r="B366" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>202210537</v>
+      </c>
+      <c r="B367" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>202510622</v>
+      </c>
+      <c r="B368" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>202502508</v>
+      </c>
+      <c r="B369" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>202102359</v>
+      </c>
+      <c r="B370" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>202511053</v>
+      </c>
+      <c r="B371" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>202503416</v>
+      </c>
+      <c r="B372" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>202503464</v>
+      </c>
+      <c r="B373" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>202206636</v>
+      </c>
+      <c r="B374" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>202205318</v>
+      </c>
+      <c r="B375" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>202502510</v>
+      </c>
+      <c r="B376" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>202511047</v>
+      </c>
+      <c r="B377" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>202205022</v>
+      </c>
+      <c r="B378" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>202512130</v>
+      </c>
+      <c r="B379" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>202204883</v>
+      </c>
+      <c r="B380" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>202108673</v>
+      </c>
+      <c r="B381" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>202207871</v>
+      </c>
+      <c r="B382" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>201902398</v>
+      </c>
+      <c r="B383" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>202208726</v>
+      </c>
+      <c r="B384" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>202511257</v>
+      </c>
+      <c r="B385" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>202108877</v>
+      </c>
+      <c r="B386" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>202409902</v>
+      </c>
+      <c r="B387" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>202204802</v>
+      </c>
+      <c r="B388" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>202211070</v>
+      </c>
+      <c r="B389" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>202514197</v>
+      </c>
+      <c r="B390" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>202510623</v>
+      </c>
+      <c r="B391" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>202502513</v>
+      </c>
+      <c r="B392" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>201906293</v>
+      </c>
+      <c r="B393" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>202206180</v>
+      </c>
+      <c r="B394" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>202208957</v>
+      </c>
+      <c r="B395" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>202108751</v>
+      </c>
+      <c r="B396" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>202512468</v>
+      </c>
+      <c r="B397" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>202503018</v>
+      </c>
+      <c r="B398" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>202409904</v>
+      </c>
+      <c r="B399" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>202500548</v>
+      </c>
+      <c r="B400" t="n">
+        <v>559659</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>202502507</v>
+      </c>
+      <c r="B401" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>202500539</v>
+      </c>
+      <c r="B402" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>202108685</v>
+      </c>
+      <c r="B403" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>202100684</v>
+      </c>
+      <c r="B404" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>202510620</v>
+      </c>
+      <c r="B405" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>202503496</v>
+      </c>
+      <c r="B406" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>202206097</v>
+      </c>
+      <c r="B407" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>200907258</v>
+      </c>
+      <c r="B408" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>202109244</v>
+      </c>
+      <c r="B409" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>202206173</v>
+      </c>
+      <c r="B410" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>202500541</v>
+      </c>
+      <c r="B411" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>202500542</v>
+      </c>
+      <c r="B412" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>202205629</v>
+      </c>
+      <c r="B413" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>202210537</v>
+      </c>
+      <c r="B414" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>202510622</v>
+      </c>
+      <c r="B415" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>202502508</v>
+      </c>
+      <c r="B416" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>202102359</v>
+      </c>
+      <c r="B417" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>202500543</v>
+      </c>
+      <c r="B418" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>202511053</v>
+      </c>
+      <c r="B419" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>202508617</v>
+      </c>
+      <c r="B420" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>202503416</v>
+      </c>
+      <c r="B421" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>202503464</v>
+      </c>
+      <c r="B422" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>202206636</v>
+      </c>
+      <c r="B423" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>202205318</v>
+      </c>
+      <c r="B424" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>202500544</v>
+      </c>
+      <c r="B425" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>202502510</v>
+      </c>
+      <c r="B426" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>202205022</v>
+      </c>
+      <c r="B427" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>202204883</v>
+      </c>
+      <c r="B428" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>202108673</v>
+      </c>
+      <c r="B429" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>202207871</v>
+      </c>
+      <c r="B430" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>202208726</v>
+      </c>
+      <c r="B431" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>202511257</v>
+      </c>
+      <c r="B432" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>202108877</v>
+      </c>
+      <c r="B433" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>202500545</v>
+      </c>
+      <c r="B434" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>202204802</v>
+      </c>
+      <c r="B435" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>201606434</v>
+      </c>
+      <c r="B436" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>202008219</v>
+      </c>
+      <c r="B437" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>202510623</v>
+      </c>
+      <c r="B438" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>201906293</v>
+      </c>
+      <c r="B439" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>202206180</v>
+      </c>
+      <c r="B440" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>202502654</v>
+      </c>
+      <c r="B441" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>202208957</v>
+      </c>
+      <c r="B442" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>202108751</v>
+      </c>
+      <c r="B443" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>202500548</v>
+      </c>
+      <c r="B444" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>202508615</v>
+      </c>
+      <c r="B445" t="n">
+        <v>559658</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>202502842</v>
+      </c>
+      <c r="B446" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>202502507</v>
+      </c>
+      <c r="B447" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>202500539</v>
+      </c>
+      <c r="B448" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>202502639</v>
+      </c>
+      <c r="B449" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>202108685</v>
+      </c>
+      <c r="B450" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>202100684</v>
+      </c>
+      <c r="B451" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>202109775</v>
+      </c>
+      <c r="B452" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>202510620</v>
+      </c>
+      <c r="B453" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>202503496</v>
+      </c>
+      <c r="B454" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>202206097</v>
+      </c>
+      <c r="B455" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>202109244</v>
+      </c>
+      <c r="B456" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>202206173</v>
+      </c>
+      <c r="B457" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>202500541</v>
+      </c>
+      <c r="B458" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>202500542</v>
+      </c>
+      <c r="B459" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>202205629</v>
+      </c>
+      <c r="B460" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>202210537</v>
+      </c>
+      <c r="B461" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>202510622</v>
+      </c>
+      <c r="B462" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>202502508</v>
+      </c>
+      <c r="B463" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>202102359</v>
+      </c>
+      <c r="B464" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>201908253</v>
+      </c>
+      <c r="B465" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>202511053</v>
+      </c>
+      <c r="B466" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>202503416</v>
+      </c>
+      <c r="B467" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>202503464</v>
+      </c>
+      <c r="B468" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>202206636</v>
+      </c>
+      <c r="B469" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>202205318</v>
+      </c>
+      <c r="B470" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>202500544</v>
+      </c>
+      <c r="B471" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>202502510</v>
+      </c>
+      <c r="B472" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>202205022</v>
+      </c>
+      <c r="B473" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>202108777</v>
+      </c>
+      <c r="B474" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>202204883</v>
+      </c>
+      <c r="B475" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>202108673</v>
+      </c>
+      <c r="B476" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>202207871</v>
+      </c>
+      <c r="B477" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>202208726</v>
+      </c>
+      <c r="B478" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>202511257</v>
+      </c>
+      <c r="B479" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>202108877</v>
+      </c>
+      <c r="B480" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>202500545</v>
+      </c>
+      <c r="B481" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>202409902</v>
+      </c>
+      <c r="B482" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>202204802</v>
+      </c>
+      <c r="B483" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>202211070</v>
+      </c>
+      <c r="B484" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>201606434</v>
+      </c>
+      <c r="B485" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>202510623</v>
+      </c>
+      <c r="B486" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>202401558</v>
+      </c>
+      <c r="B487" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>202206180</v>
+      </c>
+      <c r="B488" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>202208957</v>
+      </c>
+      <c r="B489" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>202510624</v>
+      </c>
+      <c r="B490" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>202108751</v>
+      </c>
+      <c r="B491" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>202409904</v>
+      </c>
+      <c r="B492" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>202500548</v>
+      </c>
+      <c r="B493" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>202402696</v>
+      </c>
+      <c r="B494" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>202502844</v>
+      </c>
+      <c r="B495" t="n">
+        <v>559656</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>202502507</v>
+      </c>
+      <c r="B496" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>202500539</v>
+      </c>
+      <c r="B497" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>202502639</v>
+      </c>
+      <c r="B498" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>202108685</v>
+      </c>
+      <c r="B499" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>202100684</v>
+      </c>
+      <c r="B500" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>202510620</v>
+      </c>
+      <c r="B501" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>202503496</v>
+      </c>
+      <c r="B502" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>202206097</v>
+      </c>
+      <c r="B503" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>202510621</v>
+      </c>
+      <c r="B504" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>200907258</v>
+      </c>
+      <c r="B505" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>202206173</v>
+      </c>
+      <c r="B506" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>202500541</v>
+      </c>
+      <c r="B507" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>202500542</v>
+      </c>
+      <c r="B508" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>202205629</v>
+      </c>
+      <c r="B509" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>202210537</v>
+      </c>
+      <c r="B510" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>202510622</v>
+      </c>
+      <c r="B511" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>202502508</v>
+      </c>
+      <c r="B512" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>202502841</v>
+      </c>
+      <c r="B513" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>202102359</v>
+      </c>
+      <c r="B514" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>201908253</v>
+      </c>
+      <c r="B515" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>202511053</v>
+      </c>
+      <c r="B516" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>202508617</v>
+      </c>
+      <c r="B517" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>202503416</v>
+      </c>
+      <c r="B518" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>202503464</v>
+      </c>
+      <c r="B519" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>202206636</v>
+      </c>
+      <c r="B520" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>202007851</v>
+      </c>
+      <c r="B521" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>202205318</v>
+      </c>
+      <c r="B522" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>202500544</v>
+      </c>
+      <c r="B523" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>202502510</v>
+      </c>
+      <c r="B524" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>202205022</v>
+      </c>
+      <c r="B525" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>202204883</v>
+      </c>
+      <c r="B526" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>202108673</v>
+      </c>
+      <c r="B527" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>202207871</v>
+      </c>
+      <c r="B528" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>202208726</v>
+      </c>
+      <c r="B529" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>202511257</v>
+      </c>
+      <c r="B530" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>202108877</v>
+      </c>
+      <c r="B531" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>202500545</v>
+      </c>
+      <c r="B532" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>202409902</v>
+      </c>
+      <c r="B533" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>202204802</v>
+      </c>
+      <c r="B534" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>201606434</v>
+      </c>
+      <c r="B535" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>202008219</v>
+      </c>
+      <c r="B536" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>202510623</v>
+      </c>
+      <c r="B537" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>202401558</v>
+      </c>
+      <c r="B538" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>202206180</v>
+      </c>
+      <c r="B539" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>202208957</v>
+      </c>
+      <c r="B540" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>202108751</v>
+      </c>
+      <c r="B541" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>202409904</v>
+      </c>
+      <c r="B542" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>202500548</v>
+      </c>
+      <c r="B543" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>202508615</v>
+      </c>
+      <c r="B544" t="n">
+        <v>559655</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>202502506</v>
+      </c>
+      <c r="B545" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>202502507</v>
+      </c>
+      <c r="B546" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>202500539</v>
+      </c>
+      <c r="B547" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>202108685</v>
+      </c>
+      <c r="B548" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>202100684</v>
+      </c>
+      <c r="B549" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>202510620</v>
+      </c>
+      <c r="B550" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>202503496</v>
+      </c>
+      <c r="B551" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>202206097</v>
+      </c>
+      <c r="B552" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>202510621</v>
+      </c>
+      <c r="B553" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>202206173</v>
+      </c>
+      <c r="B554" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>202500541</v>
+      </c>
+      <c r="B555" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>202500542</v>
+      </c>
+      <c r="B556" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>202205629</v>
+      </c>
+      <c r="B557" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>202210537</v>
+      </c>
+      <c r="B558" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>202510622</v>
+      </c>
+      <c r="B559" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>202502508</v>
+      </c>
+      <c r="B560" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>202102359</v>
+      </c>
+      <c r="B561" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>202500543</v>
+      </c>
+      <c r="B562" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>202511053</v>
+      </c>
+      <c r="B563" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>202503416</v>
+      </c>
+      <c r="B564" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>202503464</v>
+      </c>
+      <c r="B565" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>202206636</v>
+      </c>
+      <c r="B566" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>202007851</v>
+      </c>
+      <c r="B567" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>202205318</v>
+      </c>
+      <c r="B568" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>202500544</v>
+      </c>
+      <c r="B569" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>202502510</v>
+      </c>
+      <c r="B570" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>202205022</v>
+      </c>
+      <c r="B571" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>202204883</v>
+      </c>
+      <c r="B572" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>202108673</v>
+      </c>
+      <c r="B573" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>202207871</v>
+      </c>
+      <c r="B574" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>202208726</v>
+      </c>
+      <c r="B575" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>202511257</v>
+      </c>
+      <c r="B576" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>202108877</v>
+      </c>
+      <c r="B577" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>202500545</v>
+      </c>
+      <c r="B578" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>202409902</v>
+      </c>
+      <c r="B579" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>202204802</v>
+      </c>
+      <c r="B580" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>202211070</v>
+      </c>
+      <c r="B581" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>201606434</v>
+      </c>
+      <c r="B582" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>202510623</v>
+      </c>
+      <c r="B583" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>202401558</v>
+      </c>
+      <c r="B584" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>202206180</v>
+      </c>
+      <c r="B585" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>202208957</v>
+      </c>
+      <c r="B586" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>202510624</v>
+      </c>
+      <c r="B587" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>202108751</v>
+      </c>
+      <c r="B588" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>202409904</v>
+      </c>
+      <c r="B589" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>202500548</v>
+      </c>
+      <c r="B590" t="n">
+        <v>559654</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UC \ UC</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>PPES</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>ERMS</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>TVVS</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>LES</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>GPIE</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>CES</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>ADES</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>GQMPS</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>COSN</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>IPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PPES</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ERMS</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ADS</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TVVS</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LES</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GPIE</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CES</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ADES</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GQMPS</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>COSN</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>IPC</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/src/scrapper/database/dbs/files_csv/database_export.xlsx
+++ b/src/scrapper/database/dbs/files_csv/database_export.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-27 00:04:50.140695</t>
+          <t>2026-05-27 02:52:01.183716</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:58.456767</t>
+          <t>2026-05-27 02:53:14.302509</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:05.338492</t>
+          <t>2026-05-27 02:54:24.955608</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:41.857662</t>
+          <t>2026-05-27 02:54:00.911231</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:51.387715</t>
+          <t>2026-05-27 02:54:10.443015</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:48.262232</t>
+          <t>2026-05-27 02:54:07.524541</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:13.253627</t>
+          <t>2026-05-27 02:54:32.328892</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:02.594701</t>
+          <t>2026-05-27 02:54:22.740317</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:59.867020</t>
+          <t>2026-05-27 02:54:21.194930</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:11.125517</t>
+          <t>2026-05-27 02:54:30.154496</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:08.280126</t>
+          <t>2026-05-27 02:54:27.273643</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:32.541194</t>
+          <t>2026-05-27 02:53:49.951050</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:44.368786</t>
+          <t>2026-05-27 02:54:03.326346</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:54.158261</t>
+          <t>2026-05-27 02:54:15.273937</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:46.352006</t>
+          <t>2026-05-27 02:54:05.948788</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:52.728864</t>
+          <t>2026-05-27 02:54:12.551667</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:17.991671</t>
+          <t>2026-05-27 02:52:28.940706</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:34.908560</t>
+          <t>2026-05-27 02:52:47.549651</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:15.912765</t>
+          <t>2026-05-27 02:52:27.076081</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:20.892977</t>
+          <t>2026-05-27 02:52:31.761451</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:36.682034</t>
+          <t>2026-05-27 02:52:49.991313</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-05-27 00:04:59.038275</t>
+          <t>2026-05-27 02:52:11.311771</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:23.371751</t>
+          <t>2026-05-27 02:52:34.647879</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:34.393500</t>
+          <t>2026-05-27 02:53:52.556606</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:39.575679</t>
+          <t>2026-05-27 02:53:58.582627</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:51.092396</t>
+          <t>2026-05-27 02:53:04.852581</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:56.973612</t>
+          <t>2026-05-27 02:54:18.203853</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:09.190531</t>
+          <t>2026-05-27 02:52:21.540575</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:37.352693</t>
+          <t>2026-05-27 02:53:55.487073</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:29.863609</t>
+          <t>2026-05-27 02:53:47.449503</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:14.073506</t>
+          <t>2026-05-27 02:52:24.477548</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:11.305366</t>
+          <t>2026-05-27 02:52:22.862515</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:52.933590</t>
+          <t>2026-05-27 02:53:07.425094</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:32.146954</t>
+          <t>2026-05-27 02:52:44.738411</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:01.934987</t>
+          <t>2026-05-27 02:52:13.806336</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:47.468344</t>
+          <t>2026-05-27 02:53:00.260016</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:49.784702</t>
+          <t>2026-05-27 02:53:01.984786</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:07.197616</t>
+          <t>2026-05-27 02:52:18.504702</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:25.332207</t>
+          <t>2026-05-27 02:53:42.091062</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:21.565663</t>
+          <t>2026-05-27 02:53:36.608540</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:16.957939</t>
+          <t>2026-05-27 02:53:31.146386</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:43.307616</t>
+          <t>2026-05-27 02:52:57.356901</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:45.224030</t>
+          <t>2026-05-27 02:52:58.879640</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:00.433903</t>
+          <t>2026-05-27 02:53:17.139143</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:54.759450</t>
+          <t>2026-05-27 02:53:09.774520</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:19.656546</t>
+          <t>2026-05-27 02:53:33.991227</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:11.706432</t>
+          <t>2026-05-27 02:53:27.194941</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:38.652192</t>
+          <t>2026-05-27 02:52:52.673487</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:14.574923</t>
+          <t>2026-05-27 02:53:28.927578</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:28.782224</t>
+          <t>2026-05-27 02:52:40.187674</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:41.255353</t>
+          <t>2026-05-27 02:52:54.848542</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:05.835444</t>
+          <t>2026-05-27 02:53:22.416834</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:56.613223</t>
+          <t>2026-05-27 02:53:11.522828</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:26.381098</t>
+          <t>2026-05-27 02:52:37.565032</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:08.851398</t>
+          <t>2026-05-27 02:53:24.342191</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:22.781127</t>
+          <t>2026-05-27 02:53:39.543447</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:30.900112</t>
+          <t>2026-05-27 02:52:42.952549</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:28.190661</t>
+          <t>2026-05-27 02:53:44.754538</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-05-27 00:05:04.685371</t>
+          <t>2026-05-27 02:52:16.469775</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-05-27 00:06:03.381934</t>
+          <t>2026-05-27 02:53:19.706934</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:28.115406</t>
+          <t>2026-05-27 02:54:49.534763</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:35.254580</t>
+          <t>2026-05-27 02:54:57.384491</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:40.246313</t>
+          <t>2026-05-27 02:54:41.663732</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:22.767520</t>
+          <t>2026-05-27 02:54:44.135736</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:30.418590</t>
+          <t>2026-05-27 02:54:52.284491</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:46.946601</t>
+          <t>2026-05-27 02:55:07.263829</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:42.187682</t>
+          <t>2026-05-27 02:55:02.511751</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:51.961089</t>
+          <t>2026-05-27 02:55:10.882815</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:54.732441</t>
+          <t>2026-05-27 02:55:12.479297</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:49.650637</t>
+          <t>2026-05-27 02:55:08.957109</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:43.983589</t>
+          <t>2026-05-27 02:55:04.285146</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:57.627788</t>
+          <t>2026-05-27 02:55:15.034191</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:25.466548</t>
+          <t>2026-05-27 02:54:46.539617</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:38.175159</t>
+          <t>2026-05-27 02:55:00.159665</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-05-27 00:07:32.286336</t>
+          <t>2026-05-27 02:54:54.494020</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-27 00:04:42.259642</t>
+          <t>2026-05-27 02:51:53.296351</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3970,6 +3970,44 @@
         <is>
           <t>semester</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>36744721</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Unidades Curriculares Optativas - 2º Grupo</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10861</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>36746612</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Unidades Curriculares Optativas - 1º Grupo</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10861</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3983,7 +4021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3996,6 +4034,38 @@
         <is>
           <t>course_group_id</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>559727</v>
+      </c>
+      <c r="B2" t="n">
+        <v>36744721</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>559728</v>
+      </c>
+      <c r="B3" t="n">
+        <v>36744721</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>559663</v>
+      </c>
+      <c r="B4" t="n">
+        <v>36746612</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>559664</v>
+      </c>
+      <c r="B5" t="n">
+        <v>36746612</v>
       </c>
     </row>
   </sheetData>
@@ -4026,26 +4096,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>202502507</v>
+        <v>202502506</v>
       </c>
       <c r="B2" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>202500539</v>
+        <v>202502507</v>
       </c>
       <c r="B3" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>202208028</v>
+        <v>202500539</v>
       </c>
       <c r="B4" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="5">
@@ -4053,7 +4123,7 @@
         <v>202108685</v>
       </c>
       <c r="B5" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="6">
@@ -4061,380 +4131,380 @@
         <v>202100684</v>
       </c>
       <c r="B6" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202109775</v>
+        <v>202510620</v>
       </c>
       <c r="B7" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>202510620</v>
+        <v>202503496</v>
       </c>
       <c r="B8" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>202503496</v>
+        <v>202206097</v>
       </c>
       <c r="B9" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>202206097</v>
+        <v>202510621</v>
       </c>
       <c r="B10" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>202510621</v>
+        <v>202206173</v>
       </c>
       <c r="B11" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>200907258</v>
+        <v>202500541</v>
       </c>
       <c r="B12" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>202107100</v>
+        <v>202500542</v>
       </c>
       <c r="B13" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>202206173</v>
+        <v>202205629</v>
       </c>
       <c r="B14" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>202500541</v>
+        <v>202210537</v>
       </c>
       <c r="B15" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>202500542</v>
+        <v>202510622</v>
       </c>
       <c r="B16" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>202205629</v>
+        <v>202502508</v>
       </c>
       <c r="B17" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>202210537</v>
+        <v>202102359</v>
       </c>
       <c r="B18" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>202510622</v>
+        <v>202500543</v>
       </c>
       <c r="B19" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>202502508</v>
+        <v>202511053</v>
       </c>
       <c r="B20" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>202502841</v>
+        <v>202503416</v>
       </c>
       <c r="B21" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>202102359</v>
+        <v>202503464</v>
       </c>
       <c r="B22" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>202500543</v>
+        <v>202206636</v>
       </c>
       <c r="B23" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>202511053</v>
+        <v>202007851</v>
       </c>
       <c r="B24" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>202503416</v>
+        <v>202205318</v>
       </c>
       <c r="B25" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>202206636</v>
+        <v>202500544</v>
       </c>
       <c r="B26" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>202007851</v>
+        <v>202502510</v>
       </c>
       <c r="B27" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>202205318</v>
+        <v>202205022</v>
       </c>
       <c r="B28" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>202500544</v>
+        <v>202204883</v>
       </c>
       <c r="B29" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>202502510</v>
+        <v>202108673</v>
       </c>
       <c r="B30" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>202205022</v>
+        <v>202207871</v>
       </c>
       <c r="B31" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>202204883</v>
+        <v>202208726</v>
       </c>
       <c r="B32" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>202108673</v>
+        <v>202511257</v>
       </c>
       <c r="B33" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>202207871</v>
+        <v>202108877</v>
       </c>
       <c r="B34" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>202508437</v>
+        <v>202500545</v>
       </c>
       <c r="B35" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>202208726</v>
+        <v>202409902</v>
       </c>
       <c r="B36" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>202511257</v>
+        <v>202204802</v>
       </c>
       <c r="B37" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>202108877</v>
+        <v>202211070</v>
       </c>
       <c r="B38" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>202500545</v>
+        <v>201606434</v>
       </c>
       <c r="B39" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>202204802</v>
+        <v>202510623</v>
       </c>
       <c r="B40" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>202211070</v>
+        <v>202401558</v>
       </c>
       <c r="B41" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>201606434</v>
+        <v>202206180</v>
       </c>
       <c r="B42" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>202008219</v>
+        <v>202208957</v>
       </c>
       <c r="B43" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>202501687</v>
+        <v>202510624</v>
       </c>
       <c r="B44" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>202502849</v>
+        <v>202108751</v>
       </c>
       <c r="B45" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>202510623</v>
+        <v>202409904</v>
       </c>
       <c r="B46" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>202206180</v>
+        <v>202500548</v>
       </c>
       <c r="B47" t="n">
-        <v>559657</v>
+        <v>559654</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>202502654</v>
+        <v>202108860</v>
       </c>
       <c r="B48" t="n">
-        <v>559657</v>
+        <v>559728</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>202208957</v>
+        <v>202400068</v>
       </c>
       <c r="B49" t="n">
-        <v>559657</v>
+        <v>559728</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>202510624</v>
+        <v>201908253</v>
       </c>
       <c r="B50" t="n">
-        <v>559657</v>
+        <v>559728</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>202108751</v>
+        <v>202108879</v>
       </c>
       <c r="B51" t="n">
-        <v>559657</v>
+        <v>559728</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>202500548</v>
+        <v>202108683</v>
       </c>
       <c r="B52" t="n">
-        <v>559657</v>
+        <v>559728</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>202108860</v>
+        <v>202502849</v>
       </c>
       <c r="B53" t="n">
         <v>559728</v>
@@ -4442,7 +4512,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>202400068</v>
+        <v>202108809</v>
       </c>
       <c r="B54" t="n">
         <v>559728</v>
@@ -4450,7 +4520,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>201908253</v>
+        <v>201906293</v>
       </c>
       <c r="B55" t="n">
         <v>559728</v>
@@ -4458,7 +4528,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>202108879</v>
+        <v>202502654</v>
       </c>
       <c r="B56" t="n">
         <v>559728</v>
@@ -4466,7 +4536,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>202108683</v>
+        <v>202403111</v>
       </c>
       <c r="B57" t="n">
         <v>559728</v>
@@ -4474,47 +4544,47 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>202502849</v>
+        <v>202400071</v>
       </c>
       <c r="B58" t="n">
-        <v>559728</v>
+        <v>559727</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>202108809</v>
+        <v>202109244</v>
       </c>
       <c r="B59" t="n">
-        <v>559728</v>
+        <v>559727</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>201906293</v>
+        <v>201902431</v>
       </c>
       <c r="B60" t="n">
-        <v>559728</v>
+        <v>559727</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>202502654</v>
+        <v>202508617</v>
       </c>
       <c r="B61" t="n">
-        <v>559728</v>
+        <v>559727</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>202403111</v>
+        <v>202108693</v>
       </c>
       <c r="B62" t="n">
-        <v>559728</v>
+        <v>559727</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>202400071</v>
+        <v>202108767</v>
       </c>
       <c r="B63" t="n">
         <v>559727</v>
@@ -4522,7 +4592,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>202109244</v>
+        <v>202308712</v>
       </c>
       <c r="B64" t="n">
         <v>559727</v>
@@ -4530,7 +4600,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>201902431</v>
+        <v>202108712</v>
       </c>
       <c r="B65" t="n">
         <v>559727</v>
@@ -4538,7 +4608,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>202508617</v>
+        <v>202402636</v>
       </c>
       <c r="B66" t="n">
         <v>559727</v>
@@ -4546,7 +4616,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>202108693</v>
+        <v>201902398</v>
       </c>
       <c r="B67" t="n">
         <v>559727</v>
@@ -4554,7 +4624,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>202108767</v>
+        <v>202503094</v>
       </c>
       <c r="B68" t="n">
         <v>559727</v>
@@ -4562,7 +4632,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>202308712</v>
+        <v>202004453</v>
       </c>
       <c r="B69" t="n">
         <v>559727</v>
@@ -4570,7 +4640,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>202108712</v>
+        <v>202008219</v>
       </c>
       <c r="B70" t="n">
         <v>559727</v>
@@ -4578,7 +4648,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>202402636</v>
+        <v>201304504</v>
       </c>
       <c r="B71" t="n">
         <v>559727</v>
@@ -4586,7 +4656,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>201902398</v>
+        <v>202502849</v>
       </c>
       <c r="B72" t="n">
         <v>559727</v>
@@ -4594,7 +4664,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>202503094</v>
+        <v>202108853</v>
       </c>
       <c r="B73" t="n">
         <v>559727</v>
@@ -4602,7 +4672,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>202004453</v>
+        <v>202401669</v>
       </c>
       <c r="B74" t="n">
         <v>559727</v>
@@ -4610,7 +4680,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>202008219</v>
+        <v>202409903</v>
       </c>
       <c r="B75" t="n">
         <v>559727</v>
@@ -4618,7 +4688,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>201304504</v>
+        <v>202403077</v>
       </c>
       <c r="B76" t="n">
         <v>559727</v>
@@ -4626,7 +4696,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>202502849</v>
+        <v>202108653</v>
       </c>
       <c r="B77" t="n">
         <v>559727</v>
@@ -4634,7 +4704,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>202108853</v>
+        <v>202502654</v>
       </c>
       <c r="B78" t="n">
         <v>559727</v>
@@ -4642,7 +4712,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>202401669</v>
+        <v>202108708</v>
       </c>
       <c r="B79" t="n">
         <v>559727</v>
@@ -4650,7 +4720,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>202409903</v>
+        <v>202108807</v>
       </c>
       <c r="B80" t="n">
         <v>559727</v>
@@ -4658,7 +4728,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>202403077</v>
+        <v>202103631</v>
       </c>
       <c r="B81" t="n">
         <v>559727</v>
@@ -4666,7 +4736,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>202108653</v>
+        <v>202108681</v>
       </c>
       <c r="B82" t="n">
         <v>559727</v>
@@ -4674,7 +4744,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>202502654</v>
+        <v>202108840</v>
       </c>
       <c r="B83" t="n">
         <v>559727</v>
@@ -4682,7 +4752,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>202108708</v>
+        <v>202502844</v>
       </c>
       <c r="B84" t="n">
         <v>559727</v>
@@ -4690,7 +4760,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>202108807</v>
+        <v>202508615</v>
       </c>
       <c r="B85" t="n">
         <v>559727</v>
@@ -4698,47 +4768,47 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>202103631</v>
+        <v>202400040</v>
       </c>
       <c r="B86" t="n">
-        <v>559727</v>
+        <v>559726</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>202108681</v>
+        <v>202400071</v>
       </c>
       <c r="B87" t="n">
-        <v>559727</v>
+        <v>559726</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>202108840</v>
+        <v>202108860</v>
       </c>
       <c r="B88" t="n">
-        <v>559727</v>
+        <v>559726</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>202502844</v>
+        <v>202400068</v>
       </c>
       <c r="B89" t="n">
-        <v>559727</v>
+        <v>559726</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>202508615</v>
+        <v>202107100</v>
       </c>
       <c r="B90" t="n">
-        <v>559727</v>
+        <v>559726</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>202400040</v>
+        <v>202400037</v>
       </c>
       <c r="B91" t="n">
         <v>559726</v>
@@ -4746,7 +4816,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>202400071</v>
+        <v>201908253</v>
       </c>
       <c r="B92" t="n">
         <v>559726</v>
@@ -4754,7 +4824,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>202108860</v>
+        <v>202108693</v>
       </c>
       <c r="B93" t="n">
         <v>559726</v>
@@ -4762,7 +4832,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>202400068</v>
+        <v>202108767</v>
       </c>
       <c r="B94" t="n">
         <v>559726</v>
@@ -4770,7 +4840,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>202107100</v>
+        <v>202308712</v>
       </c>
       <c r="B95" t="n">
         <v>559726</v>
@@ -4778,7 +4848,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>202400037</v>
+        <v>202108737</v>
       </c>
       <c r="B96" t="n">
         <v>559726</v>
@@ -4786,7 +4856,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>201908253</v>
+        <v>202108848</v>
       </c>
       <c r="B97" t="n">
         <v>559726</v>
@@ -4794,7 +4864,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>202108693</v>
+        <v>202108879</v>
       </c>
       <c r="B98" t="n">
         <v>559726</v>
@@ -4802,7 +4872,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>202108767</v>
+        <v>202108712</v>
       </c>
       <c r="B99" t="n">
         <v>559726</v>
@@ -4810,7 +4880,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>202308712</v>
+        <v>202402636</v>
       </c>
       <c r="B100" t="n">
         <v>559726</v>
@@ -4818,7 +4888,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>202108737</v>
+        <v>202302527</v>
       </c>
       <c r="B101" t="n">
         <v>559726</v>
@@ -4826,7 +4896,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>202108848</v>
+        <v>201902398</v>
       </c>
       <c r="B102" t="n">
         <v>559726</v>
@@ -4834,7 +4904,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>202108879</v>
+        <v>202108683</v>
       </c>
       <c r="B103" t="n">
         <v>559726</v>
@@ -4842,7 +4912,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>202108712</v>
+        <v>202004453</v>
       </c>
       <c r="B104" t="n">
         <v>559726</v>
@@ -4850,7 +4920,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>202402636</v>
+        <v>202008219</v>
       </c>
       <c r="B105" t="n">
         <v>559726</v>
@@ -4858,7 +4928,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>202302527</v>
+        <v>201304504</v>
       </c>
       <c r="B106" t="n">
         <v>559726</v>
@@ -4866,7 +4936,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>201902398</v>
+        <v>202108853</v>
       </c>
       <c r="B107" t="n">
         <v>559726</v>
@@ -4874,7 +4944,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>202108683</v>
+        <v>202401669</v>
       </c>
       <c r="B108" t="n">
         <v>559726</v>
@@ -4882,7 +4952,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>202004453</v>
+        <v>202409903</v>
       </c>
       <c r="B109" t="n">
         <v>559726</v>
@@ -4890,7 +4960,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>202008219</v>
+        <v>202108809</v>
       </c>
       <c r="B110" t="n">
         <v>559726</v>
@@ -4898,7 +4968,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>201304504</v>
+        <v>202403077</v>
       </c>
       <c r="B111" t="n">
         <v>559726</v>
@@ -4906,7 +4976,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>202108853</v>
+        <v>202108653</v>
       </c>
       <c r="B112" t="n">
         <v>559726</v>
@@ -4914,7 +4984,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>202401669</v>
+        <v>202108756</v>
       </c>
       <c r="B113" t="n">
         <v>559726</v>
@@ -4922,7 +4992,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>202409903</v>
+        <v>201906293</v>
       </c>
       <c r="B114" t="n">
         <v>559726</v>
@@ -4930,7 +5000,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>202108809</v>
+        <v>202103337</v>
       </c>
       <c r="B115" t="n">
         <v>559726</v>
@@ -4938,7 +5008,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>202403077</v>
+        <v>202108708</v>
       </c>
       <c r="B116" t="n">
         <v>559726</v>
@@ -4946,7 +5016,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>202108653</v>
+        <v>202108807</v>
       </c>
       <c r="B117" t="n">
         <v>559726</v>
@@ -4954,7 +5024,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>202108756</v>
+        <v>202103631</v>
       </c>
       <c r="B118" t="n">
         <v>559726</v>
@@ -4962,7 +5032,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>201906293</v>
+        <v>202302522</v>
       </c>
       <c r="B119" t="n">
         <v>559726</v>
@@ -4970,7 +5040,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>202103337</v>
+        <v>202108681</v>
       </c>
       <c r="B120" t="n">
         <v>559726</v>
@@ -4978,7 +5048,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>202108708</v>
+        <v>202403111</v>
       </c>
       <c r="B121" t="n">
         <v>559726</v>
@@ -4986,7 +5056,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>202108807</v>
+        <v>202108840</v>
       </c>
       <c r="B122" t="n">
         <v>559726</v>
@@ -4994,7 +5064,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>202103631</v>
+        <v>202400393</v>
       </c>
       <c r="B123" t="n">
         <v>559726</v>
@@ -5002,7 +5072,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>202302522</v>
+        <v>202402696</v>
       </c>
       <c r="B124" t="n">
         <v>559726</v>
@@ -5010,47 +5080,47 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>202108681</v>
+        <v>202400040</v>
       </c>
       <c r="B125" t="n">
-        <v>559726</v>
+        <v>559725</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>202403111</v>
+        <v>202400071</v>
       </c>
       <c r="B126" t="n">
-        <v>559726</v>
+        <v>559725</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>202108840</v>
+        <v>202108860</v>
       </c>
       <c r="B127" t="n">
-        <v>559726</v>
+        <v>559725</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>202400393</v>
+        <v>202108745</v>
       </c>
       <c r="B128" t="n">
-        <v>559726</v>
+        <v>559725</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>202402696</v>
+        <v>202400068</v>
       </c>
       <c r="B129" t="n">
-        <v>559726</v>
+        <v>559725</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>202400040</v>
+        <v>202107100</v>
       </c>
       <c r="B130" t="n">
         <v>559725</v>
@@ -5058,7 +5128,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>202400071</v>
+        <v>202400037</v>
       </c>
       <c r="B131" t="n">
         <v>559725</v>
@@ -5066,7 +5136,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>202108860</v>
+        <v>202108693</v>
       </c>
       <c r="B132" t="n">
         <v>559725</v>
@@ -5074,7 +5144,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>202108745</v>
+        <v>202108767</v>
       </c>
       <c r="B133" t="n">
         <v>559725</v>
@@ -5082,7 +5152,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>202400068</v>
+        <v>202308712</v>
       </c>
       <c r="B134" t="n">
         <v>559725</v>
@@ -5090,7 +5160,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>202107100</v>
+        <v>202108737</v>
       </c>
       <c r="B135" t="n">
         <v>559725</v>
@@ -5098,7 +5168,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>202400037</v>
+        <v>202108848</v>
       </c>
       <c r="B136" t="n">
         <v>559725</v>
@@ -5106,7 +5176,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>202108693</v>
+        <v>202108879</v>
       </c>
       <c r="B137" t="n">
         <v>559725</v>
@@ -5114,7 +5184,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>202108767</v>
+        <v>202108712</v>
       </c>
       <c r="B138" t="n">
         <v>559725</v>
@@ -5122,7 +5192,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>202308712</v>
+        <v>202402636</v>
       </c>
       <c r="B139" t="n">
         <v>559725</v>
@@ -5130,7 +5200,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>202108737</v>
+        <v>202302527</v>
       </c>
       <c r="B140" t="n">
         <v>559725</v>
@@ -5138,7 +5208,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>202108848</v>
+        <v>201902398</v>
       </c>
       <c r="B141" t="n">
         <v>559725</v>
@@ -5146,7 +5216,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>202108879</v>
+        <v>202108683</v>
       </c>
       <c r="B142" t="n">
         <v>559725</v>
@@ -5154,7 +5224,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>202108712</v>
+        <v>202004453</v>
       </c>
       <c r="B143" t="n">
         <v>559725</v>
@@ -5162,7 +5232,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>202402636</v>
+        <v>201304504</v>
       </c>
       <c r="B144" t="n">
         <v>559725</v>
@@ -5170,7 +5240,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>202302527</v>
+        <v>202108853</v>
       </c>
       <c r="B145" t="n">
         <v>559725</v>
@@ -5178,7 +5248,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>201902398</v>
+        <v>202401669</v>
       </c>
       <c r="B146" t="n">
         <v>559725</v>
@@ -5186,7 +5256,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>202108683</v>
+        <v>202409903</v>
       </c>
       <c r="B147" t="n">
         <v>559725</v>
@@ -5194,7 +5264,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>202004453</v>
+        <v>202108809</v>
       </c>
       <c r="B148" t="n">
         <v>559725</v>
@@ -5202,7 +5272,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>201304504</v>
+        <v>202403077</v>
       </c>
       <c r="B149" t="n">
         <v>559725</v>
@@ -5210,7 +5280,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>202108853</v>
+        <v>202108653</v>
       </c>
       <c r="B150" t="n">
         <v>559725</v>
@@ -5218,7 +5288,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>202401669</v>
+        <v>202108756</v>
       </c>
       <c r="B151" t="n">
         <v>559725</v>
@@ -5226,7 +5296,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>202409903</v>
+        <v>201906293</v>
       </c>
       <c r="B152" t="n">
         <v>559725</v>
@@ -5234,7 +5304,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>202108809</v>
+        <v>202103337</v>
       </c>
       <c r="B153" t="n">
         <v>559725</v>
@@ -5242,7 +5312,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>202403077</v>
+        <v>202302862</v>
       </c>
       <c r="B154" t="n">
         <v>559725</v>
@@ -5250,7 +5320,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>202108653</v>
+        <v>202108708</v>
       </c>
       <c r="B155" t="n">
         <v>559725</v>
@@ -5258,7 +5328,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>202108756</v>
+        <v>202108807</v>
       </c>
       <c r="B156" t="n">
         <v>559725</v>
@@ -5266,7 +5336,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>201906293</v>
+        <v>202103631</v>
       </c>
       <c r="B157" t="n">
         <v>559725</v>
@@ -5274,7 +5344,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>202103337</v>
+        <v>202001957</v>
       </c>
       <c r="B158" t="n">
         <v>559725</v>
@@ -5282,7 +5352,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>202302862</v>
+        <v>202302522</v>
       </c>
       <c r="B159" t="n">
         <v>559725</v>
@@ -5290,7 +5360,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>202108708</v>
+        <v>202300431</v>
       </c>
       <c r="B160" t="n">
         <v>559725</v>
@@ -5298,7 +5368,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>202108807</v>
+        <v>202108681</v>
       </c>
       <c r="B161" t="n">
         <v>559725</v>
@@ -5306,7 +5376,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>202103631</v>
+        <v>202403111</v>
       </c>
       <c r="B162" t="n">
         <v>559725</v>
@@ -5314,7 +5384,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>202001957</v>
+        <v>202108840</v>
       </c>
       <c r="B163" t="n">
         <v>559725</v>
@@ -5322,7 +5392,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>202302522</v>
+        <v>202400393</v>
       </c>
       <c r="B164" t="n">
         <v>559725</v>
@@ -5330,7 +5400,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>202300431</v>
+        <v>202402696</v>
       </c>
       <c r="B165" t="n">
         <v>559725</v>
@@ -5338,47 +5408,47 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>202108681</v>
+        <v>202108685</v>
       </c>
       <c r="B166" t="n">
-        <v>559725</v>
+        <v>559664</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>202403111</v>
+        <v>202511830</v>
       </c>
       <c r="B167" t="n">
-        <v>559725</v>
+        <v>559664</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>202108840</v>
+        <v>202206097</v>
       </c>
       <c r="B168" t="n">
-        <v>559725</v>
+        <v>559664</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>202400393</v>
+        <v>200907258</v>
       </c>
       <c r="B169" t="n">
-        <v>559725</v>
+        <v>559664</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>202402696</v>
+        <v>202109244</v>
       </c>
       <c r="B170" t="n">
-        <v>559725</v>
+        <v>559664</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>202108685</v>
+        <v>202500541</v>
       </c>
       <c r="B171" t="n">
         <v>559664</v>
@@ -5386,7 +5456,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>202511830</v>
+        <v>202500542</v>
       </c>
       <c r="B172" t="n">
         <v>559664</v>
@@ -5394,7 +5464,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>202206097</v>
+        <v>202205629</v>
       </c>
       <c r="B173" t="n">
         <v>559664</v>
@@ -5402,7 +5472,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>200907258</v>
+        <v>202510622</v>
       </c>
       <c r="B174" t="n">
         <v>559664</v>
@@ -5410,7 +5480,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>202109244</v>
+        <v>202511053</v>
       </c>
       <c r="B175" t="n">
         <v>559664</v>
@@ -5418,7 +5488,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>202500541</v>
+        <v>202503464</v>
       </c>
       <c r="B176" t="n">
         <v>559664</v>
@@ -5426,7 +5496,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>202500542</v>
+        <v>202205318</v>
       </c>
       <c r="B177" t="n">
         <v>559664</v>
@@ -5434,7 +5504,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>202205629</v>
+        <v>202502510</v>
       </c>
       <c r="B178" t="n">
         <v>559664</v>
@@ -5442,7 +5512,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>202510622</v>
+        <v>202108673</v>
       </c>
       <c r="B179" t="n">
         <v>559664</v>
@@ -5450,7 +5520,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>202511053</v>
+        <v>202511257</v>
       </c>
       <c r="B180" t="n">
         <v>559664</v>
@@ -5458,7 +5528,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>202503464</v>
+        <v>202108877</v>
       </c>
       <c r="B181" t="n">
         <v>559664</v>
@@ -5466,7 +5536,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>202205318</v>
+        <v>202409902</v>
       </c>
       <c r="B182" t="n">
         <v>559664</v>
@@ -5474,7 +5544,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>202502510</v>
+        <v>202204802</v>
       </c>
       <c r="B183" t="n">
         <v>559664</v>
@@ -5482,7 +5552,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>202108673</v>
+        <v>202510623</v>
       </c>
       <c r="B184" t="n">
         <v>559664</v>
@@ -5490,7 +5560,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>202511257</v>
+        <v>202401558</v>
       </c>
       <c r="B185" t="n">
         <v>559664</v>
@@ -5498,7 +5568,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>202108877</v>
+        <v>202409904</v>
       </c>
       <c r="B186" t="n">
         <v>559664</v>
@@ -5506,7 +5576,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>202409902</v>
+        <v>202500548</v>
       </c>
       <c r="B187" t="n">
         <v>559664</v>
@@ -5514,47 +5584,47 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>202204802</v>
+        <v>202502507</v>
       </c>
       <c r="B188" t="n">
-        <v>559664</v>
+        <v>559663</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>202510623</v>
+        <v>202103420</v>
       </c>
       <c r="B189" t="n">
-        <v>559664</v>
+        <v>559663</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>202401558</v>
+        <v>202500539</v>
       </c>
       <c r="B190" t="n">
-        <v>559664</v>
+        <v>559663</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>202409904</v>
+        <v>202100684</v>
       </c>
       <c r="B191" t="n">
-        <v>559664</v>
+        <v>559663</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>202500548</v>
+        <v>202510620</v>
       </c>
       <c r="B192" t="n">
-        <v>559664</v>
+        <v>559663</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>202502507</v>
+        <v>202503496</v>
       </c>
       <c r="B193" t="n">
         <v>559663</v>
@@ -5562,7 +5632,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>202103420</v>
+        <v>202206173</v>
       </c>
       <c r="B194" t="n">
         <v>559663</v>
@@ -5570,7 +5640,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>202500539</v>
+        <v>202210537</v>
       </c>
       <c r="B195" t="n">
         <v>559663</v>
@@ -5578,7 +5648,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>202100684</v>
+        <v>202502508</v>
       </c>
       <c r="B196" t="n">
         <v>559663</v>
@@ -5586,7 +5656,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>202510620</v>
+        <v>202503416</v>
       </c>
       <c r="B197" t="n">
         <v>559663</v>
@@ -5594,7 +5664,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>202503496</v>
+        <v>202206636</v>
       </c>
       <c r="B198" t="n">
         <v>559663</v>
@@ -5602,7 +5672,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>202206173</v>
+        <v>202511047</v>
       </c>
       <c r="B199" t="n">
         <v>559663</v>
@@ -5610,7 +5680,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>202210537</v>
+        <v>202205022</v>
       </c>
       <c r="B200" t="n">
         <v>559663</v>
@@ -5618,7 +5688,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>202502508</v>
+        <v>202204883</v>
       </c>
       <c r="B201" t="n">
         <v>559663</v>
@@ -5626,7 +5696,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>202503416</v>
+        <v>202207871</v>
       </c>
       <c r="B202" t="n">
         <v>559663</v>
@@ -5634,7 +5704,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>202206636</v>
+        <v>202208726</v>
       </c>
       <c r="B203" t="n">
         <v>559663</v>
@@ -5642,7 +5712,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>202511047</v>
+        <v>202500545</v>
       </c>
       <c r="B204" t="n">
         <v>559663</v>
@@ -5650,7 +5720,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>202205022</v>
+        <v>202514197</v>
       </c>
       <c r="B205" t="n">
         <v>559663</v>
@@ -5658,7 +5728,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>202204883</v>
+        <v>202502513</v>
       </c>
       <c r="B206" t="n">
         <v>559663</v>
@@ -5666,7 +5736,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>202207871</v>
+        <v>202206180</v>
       </c>
       <c r="B207" t="n">
         <v>559663</v>
@@ -5674,7 +5744,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>202208726</v>
+        <v>202208957</v>
       </c>
       <c r="B208" t="n">
         <v>559663</v>
@@ -5682,7 +5752,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>202500545</v>
+        <v>202512262</v>
       </c>
       <c r="B209" t="n">
         <v>559663</v>
@@ -5690,7 +5760,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>202514197</v>
+        <v>202108751</v>
       </c>
       <c r="B210" t="n">
         <v>559663</v>
@@ -5698,47 +5768,47 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>202502513</v>
+        <v>202502506</v>
       </c>
       <c r="B211" t="n">
-        <v>559663</v>
+        <v>559662</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>202206180</v>
+        <v>202502507</v>
       </c>
       <c r="B212" t="n">
-        <v>559663</v>
+        <v>559662</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>202208957</v>
+        <v>202500539</v>
       </c>
       <c r="B213" t="n">
-        <v>559663</v>
+        <v>559662</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>202512262</v>
+        <v>202108685</v>
       </c>
       <c r="B214" t="n">
-        <v>559663</v>
+        <v>559662</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>202108751</v>
+        <v>202100684</v>
       </c>
       <c r="B215" t="n">
-        <v>559663</v>
+        <v>559662</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>202502506</v>
+        <v>202510620</v>
       </c>
       <c r="B216" t="n">
         <v>559662</v>
@@ -5746,7 +5816,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>202502507</v>
+        <v>202503496</v>
       </c>
       <c r="B217" t="n">
         <v>559662</v>
@@ -5754,7 +5824,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>202500539</v>
+        <v>202206097</v>
       </c>
       <c r="B218" t="n">
         <v>559662</v>
@@ -5762,7 +5832,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>202108685</v>
+        <v>202510621</v>
       </c>
       <c r="B219" t="n">
         <v>559662</v>
@@ -5770,7 +5840,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>202100684</v>
+        <v>200907258</v>
       </c>
       <c r="B220" t="n">
         <v>559662</v>
@@ -5778,7 +5848,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>202510620</v>
+        <v>202206173</v>
       </c>
       <c r="B221" t="n">
         <v>559662</v>
@@ -5786,7 +5856,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>202503496</v>
+        <v>202500541</v>
       </c>
       <c r="B222" t="n">
         <v>559662</v>
@@ -5794,7 +5864,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>202206097</v>
+        <v>202500542</v>
       </c>
       <c r="B223" t="n">
         <v>559662</v>
@@ -5802,7 +5872,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>202510621</v>
+        <v>202205629</v>
       </c>
       <c r="B224" t="n">
         <v>559662</v>
@@ -5810,7 +5880,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>200907258</v>
+        <v>202210537</v>
       </c>
       <c r="B225" t="n">
         <v>559662</v>
@@ -5818,7 +5888,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>202206173</v>
+        <v>202510622</v>
       </c>
       <c r="B226" t="n">
         <v>559662</v>
@@ -5826,7 +5896,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>202500541</v>
+        <v>202502508</v>
       </c>
       <c r="B227" t="n">
         <v>559662</v>
@@ -5834,7 +5904,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>202500542</v>
+        <v>202102359</v>
       </c>
       <c r="B228" t="n">
         <v>559662</v>
@@ -5842,7 +5912,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>202205629</v>
+        <v>202500543</v>
       </c>
       <c r="B229" t="n">
         <v>559662</v>
@@ -5850,7 +5920,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>202210537</v>
+        <v>202511053</v>
       </c>
       <c r="B230" t="n">
         <v>559662</v>
@@ -5858,7 +5928,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>202510622</v>
+        <v>202503416</v>
       </c>
       <c r="B231" t="n">
         <v>559662</v>
@@ -5866,7 +5936,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>202502508</v>
+        <v>202503464</v>
       </c>
       <c r="B232" t="n">
         <v>559662</v>
@@ -5874,7 +5944,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>202102359</v>
+        <v>202206636</v>
       </c>
       <c r="B233" t="n">
         <v>559662</v>
@@ -5882,7 +5952,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>202500543</v>
+        <v>202007851</v>
       </c>
       <c r="B234" t="n">
         <v>559662</v>
@@ -5890,7 +5960,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>202511053</v>
+        <v>202205318</v>
       </c>
       <c r="B235" t="n">
         <v>559662</v>
@@ -5898,7 +5968,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>202503416</v>
+        <v>202502510</v>
       </c>
       <c r="B236" t="n">
         <v>559662</v>
@@ -5906,7 +5976,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>202503464</v>
+        <v>202511047</v>
       </c>
       <c r="B237" t="n">
         <v>559662</v>
@@ -5914,7 +5984,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>202206636</v>
+        <v>202205022</v>
       </c>
       <c r="B238" t="n">
         <v>559662</v>
@@ -5922,7 +5992,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>202007851</v>
+        <v>202512130</v>
       </c>
       <c r="B239" t="n">
         <v>559662</v>
@@ -5930,7 +6000,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>202205318</v>
+        <v>202204883</v>
       </c>
       <c r="B240" t="n">
         <v>559662</v>
@@ -5938,7 +6008,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>202502510</v>
+        <v>202108673</v>
       </c>
       <c r="B241" t="n">
         <v>559662</v>
@@ -5946,7 +6016,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>202511047</v>
+        <v>202207871</v>
       </c>
       <c r="B242" t="n">
         <v>559662</v>
@@ -5954,7 +6024,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>202205022</v>
+        <v>202208726</v>
       </c>
       <c r="B243" t="n">
         <v>559662</v>
@@ -5962,7 +6032,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>202512130</v>
+        <v>202511257</v>
       </c>
       <c r="B244" t="n">
         <v>559662</v>
@@ -5970,7 +6040,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>202204883</v>
+        <v>202108877</v>
       </c>
       <c r="B245" t="n">
         <v>559662</v>
@@ -5978,7 +6048,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>202108673</v>
+        <v>202409902</v>
       </c>
       <c r="B246" t="n">
         <v>559662</v>
@@ -5986,7 +6056,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>202207871</v>
+        <v>202204802</v>
       </c>
       <c r="B247" t="n">
         <v>559662</v>
@@ -5994,7 +6064,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>202208726</v>
+        <v>202514197</v>
       </c>
       <c r="B248" t="n">
         <v>559662</v>
@@ -6002,7 +6072,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>202511257</v>
+        <v>202510623</v>
       </c>
       <c r="B249" t="n">
         <v>559662</v>
@@ -6010,7 +6080,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>202108877</v>
+        <v>202502513</v>
       </c>
       <c r="B250" t="n">
         <v>559662</v>
@@ -6018,7 +6088,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>202409902</v>
+        <v>202206180</v>
       </c>
       <c r="B251" t="n">
         <v>559662</v>
@@ -6026,7 +6096,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>202204802</v>
+        <v>202208957</v>
       </c>
       <c r="B252" t="n">
         <v>559662</v>
@@ -6034,7 +6104,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>202514197</v>
+        <v>202510624</v>
       </c>
       <c r="B253" t="n">
         <v>559662</v>
@@ -6042,7 +6112,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>202510623</v>
+        <v>202108751</v>
       </c>
       <c r="B254" t="n">
         <v>559662</v>
@@ -6050,7 +6120,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>202502513</v>
+        <v>202409904</v>
       </c>
       <c r="B255" t="n">
         <v>559662</v>
@@ -6058,7 +6128,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>202206180</v>
+        <v>202500548</v>
       </c>
       <c r="B256" t="n">
         <v>559662</v>
@@ -6066,47 +6136,47 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>202208957</v>
+        <v>202502506</v>
       </c>
       <c r="B257" t="n">
-        <v>559662</v>
+        <v>559661</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>202510624</v>
+        <v>202502507</v>
       </c>
       <c r="B258" t="n">
-        <v>559662</v>
+        <v>559661</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>202108751</v>
+        <v>202500539</v>
       </c>
       <c r="B259" t="n">
-        <v>559662</v>
+        <v>559661</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>202409904</v>
+        <v>202108685</v>
       </c>
       <c r="B260" t="n">
-        <v>559662</v>
+        <v>559661</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>202500548</v>
+        <v>202100684</v>
       </c>
       <c r="B261" t="n">
-        <v>559662</v>
+        <v>559661</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>202502506</v>
+        <v>202109775</v>
       </c>
       <c r="B262" t="n">
         <v>559661</v>
@@ -6114,7 +6184,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>202502507</v>
+        <v>202510620</v>
       </c>
       <c r="B263" t="n">
         <v>559661</v>
@@ -6122,7 +6192,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>202500539</v>
+        <v>202503496</v>
       </c>
       <c r="B264" t="n">
         <v>559661</v>
@@ -6130,7 +6200,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>202108685</v>
+        <v>202206097</v>
       </c>
       <c r="B265" t="n">
         <v>559661</v>
@@ -6138,7 +6208,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>202100684</v>
+        <v>202510621</v>
       </c>
       <c r="B266" t="n">
         <v>559661</v>
@@ -6146,7 +6216,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>202109775</v>
+        <v>202109244</v>
       </c>
       <c r="B267" t="n">
         <v>559661</v>
@@ -6154,7 +6224,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>202510620</v>
+        <v>202206173</v>
       </c>
       <c r="B268" t="n">
         <v>559661</v>
@@ -6162,7 +6232,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>202503496</v>
+        <v>202500541</v>
       </c>
       <c r="B269" t="n">
         <v>559661</v>
@@ -6170,7 +6240,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>202206097</v>
+        <v>201902431</v>
       </c>
       <c r="B270" t="n">
         <v>559661</v>
@@ -6178,7 +6248,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>202510621</v>
+        <v>202500542</v>
       </c>
       <c r="B271" t="n">
         <v>559661</v>
@@ -6186,7 +6256,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>202109244</v>
+        <v>202205629</v>
       </c>
       <c r="B272" t="n">
         <v>559661</v>
@@ -6194,7 +6264,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>202206173</v>
+        <v>202210537</v>
       </c>
       <c r="B273" t="n">
         <v>559661</v>
@@ -6202,7 +6272,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>202500541</v>
+        <v>202510622</v>
       </c>
       <c r="B274" t="n">
         <v>559661</v>
@@ -6210,7 +6280,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>201902431</v>
+        <v>202502508</v>
       </c>
       <c r="B275" t="n">
         <v>559661</v>
@@ -6218,7 +6288,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>202500542</v>
+        <v>202102359</v>
       </c>
       <c r="B276" t="n">
         <v>559661</v>
@@ -6226,7 +6296,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>202205629</v>
+        <v>202500543</v>
       </c>
       <c r="B277" t="n">
         <v>559661</v>
@@ -6234,7 +6304,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>202210537</v>
+        <v>202511053</v>
       </c>
       <c r="B278" t="n">
         <v>559661</v>
@@ -6242,7 +6312,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>202510622</v>
+        <v>202503416</v>
       </c>
       <c r="B279" t="n">
         <v>559661</v>
@@ -6250,7 +6320,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>202502508</v>
+        <v>202503464</v>
       </c>
       <c r="B280" t="n">
         <v>559661</v>
@@ -6258,7 +6328,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>202102359</v>
+        <v>202206636</v>
       </c>
       <c r="B281" t="n">
         <v>559661</v>
@@ -6266,7 +6336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>202500543</v>
+        <v>202007851</v>
       </c>
       <c r="B282" t="n">
         <v>559661</v>
@@ -6274,7 +6344,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>202511053</v>
+        <v>202205318</v>
       </c>
       <c r="B283" t="n">
         <v>559661</v>
@@ -6282,7 +6352,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>202503416</v>
+        <v>202502510</v>
       </c>
       <c r="B284" t="n">
         <v>559661</v>
@@ -6290,7 +6360,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>202503464</v>
+        <v>202511047</v>
       </c>
       <c r="B285" t="n">
         <v>559661</v>
@@ -6298,7 +6368,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>202206636</v>
+        <v>202205022</v>
       </c>
       <c r="B286" t="n">
         <v>559661</v>
@@ -6306,7 +6376,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>202007851</v>
+        <v>202204883</v>
       </c>
       <c r="B287" t="n">
         <v>559661</v>
@@ -6314,7 +6384,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>202205318</v>
+        <v>202108673</v>
       </c>
       <c r="B288" t="n">
         <v>559661</v>
@@ -6322,7 +6392,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>202502510</v>
+        <v>202207871</v>
       </c>
       <c r="B289" t="n">
         <v>559661</v>
@@ -6330,7 +6400,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>202511047</v>
+        <v>202503094</v>
       </c>
       <c r="B290" t="n">
         <v>559661</v>
@@ -6338,7 +6408,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>202205022</v>
+        <v>202208726</v>
       </c>
       <c r="B291" t="n">
         <v>559661</v>
@@ -6346,7 +6416,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>202204883</v>
+        <v>202511257</v>
       </c>
       <c r="B292" t="n">
         <v>559661</v>
@@ -6354,7 +6424,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>202108673</v>
+        <v>202108877</v>
       </c>
       <c r="B293" t="n">
         <v>559661</v>
@@ -6362,7 +6432,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>202207871</v>
+        <v>202204802</v>
       </c>
       <c r="B294" t="n">
         <v>559661</v>
@@ -6370,7 +6440,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>202503094</v>
+        <v>202211070</v>
       </c>
       <c r="B295" t="n">
         <v>559661</v>
@@ -6378,7 +6448,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>202208726</v>
+        <v>202514197</v>
       </c>
       <c r="B296" t="n">
         <v>559661</v>
@@ -6386,7 +6456,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>202511257</v>
+        <v>202510623</v>
       </c>
       <c r="B297" t="n">
         <v>559661</v>
@@ -6394,7 +6464,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>202108877</v>
+        <v>202401558</v>
       </c>
       <c r="B298" t="n">
         <v>559661</v>
@@ -6402,7 +6472,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>202204802</v>
+        <v>202502513</v>
       </c>
       <c r="B299" t="n">
         <v>559661</v>
@@ -6410,7 +6480,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>202211070</v>
+        <v>202206180</v>
       </c>
       <c r="B300" t="n">
         <v>559661</v>
@@ -6418,7 +6488,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>202514197</v>
+        <v>202208957</v>
       </c>
       <c r="B301" t="n">
         <v>559661</v>
@@ -6426,7 +6496,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>202510623</v>
+        <v>202510624</v>
       </c>
       <c r="B302" t="n">
         <v>559661</v>
@@ -6434,7 +6504,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>202401558</v>
+        <v>202108751</v>
       </c>
       <c r="B303" t="n">
         <v>559661</v>
@@ -6442,7 +6512,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>202502513</v>
+        <v>202204180</v>
       </c>
       <c r="B304" t="n">
         <v>559661</v>
@@ -6450,7 +6520,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>202206180</v>
+        <v>202500548</v>
       </c>
       <c r="B305" t="n">
         <v>559661</v>
@@ -6458,47 +6528,47 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>202208957</v>
+        <v>202502507</v>
       </c>
       <c r="B306" t="n">
-        <v>559661</v>
+        <v>559660</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>202510624</v>
+        <v>202500539</v>
       </c>
       <c r="B307" t="n">
-        <v>559661</v>
+        <v>559660</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>202108751</v>
+        <v>202108685</v>
       </c>
       <c r="B308" t="n">
-        <v>559661</v>
+        <v>559660</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>202204180</v>
+        <v>202100684</v>
       </c>
       <c r="B309" t="n">
-        <v>559661</v>
+        <v>559660</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>202500548</v>
+        <v>202109775</v>
       </c>
       <c r="B310" t="n">
-        <v>559661</v>
+        <v>559660</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>202502507</v>
+        <v>202510620</v>
       </c>
       <c r="B311" t="n">
         <v>559660</v>
@@ -6506,7 +6576,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>202500539</v>
+        <v>202503496</v>
       </c>
       <c r="B312" t="n">
         <v>559660</v>
@@ -6514,7 +6584,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>202108685</v>
+        <v>202206097</v>
       </c>
       <c r="B313" t="n">
         <v>559660</v>
@@ -6522,7 +6592,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>202100684</v>
+        <v>202510621</v>
       </c>
       <c r="B314" t="n">
         <v>559660</v>
@@ -6530,7 +6600,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>202109775</v>
+        <v>200907258</v>
       </c>
       <c r="B315" t="n">
         <v>559660</v>
@@ -6538,7 +6608,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>202510620</v>
+        <v>202206173</v>
       </c>
       <c r="B316" t="n">
         <v>559660</v>
@@ -6546,7 +6616,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>202503496</v>
+        <v>202500541</v>
       </c>
       <c r="B317" t="n">
         <v>559660</v>
@@ -6554,7 +6624,7 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>202206097</v>
+        <v>202500542</v>
       </c>
       <c r="B318" t="n">
         <v>559660</v>
@@ -6562,7 +6632,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>202510621</v>
+        <v>202205629</v>
       </c>
       <c r="B319" t="n">
         <v>559660</v>
@@ -6570,7 +6640,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>200907258</v>
+        <v>202210537</v>
       </c>
       <c r="B320" t="n">
         <v>559660</v>
@@ -6578,7 +6648,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>202206173</v>
+        <v>202510622</v>
       </c>
       <c r="B321" t="n">
         <v>559660</v>
@@ -6586,7 +6656,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>202500541</v>
+        <v>202502508</v>
       </c>
       <c r="B322" t="n">
         <v>559660</v>
@@ -6594,7 +6664,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>202500542</v>
+        <v>202102359</v>
       </c>
       <c r="B323" t="n">
         <v>559660</v>
@@ -6602,7 +6672,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>202205629</v>
+        <v>202500543</v>
       </c>
       <c r="B324" t="n">
         <v>559660</v>
@@ -6610,7 +6680,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>202210537</v>
+        <v>202511053</v>
       </c>
       <c r="B325" t="n">
         <v>559660</v>
@@ -6618,7 +6688,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>202510622</v>
+        <v>202503416</v>
       </c>
       <c r="B326" t="n">
         <v>559660</v>
@@ -6626,7 +6696,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>202502508</v>
+        <v>202503464</v>
       </c>
       <c r="B327" t="n">
         <v>559660</v>
@@ -6634,7 +6704,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>202102359</v>
+        <v>202206636</v>
       </c>
       <c r="B328" t="n">
         <v>559660</v>
@@ -6642,7 +6712,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>202500543</v>
+        <v>202007851</v>
       </c>
       <c r="B329" t="n">
         <v>559660</v>
@@ -6650,7 +6720,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>202511053</v>
+        <v>202205318</v>
       </c>
       <c r="B330" t="n">
         <v>559660</v>
@@ -6658,7 +6728,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>202503416</v>
+        <v>202502510</v>
       </c>
       <c r="B331" t="n">
         <v>559660</v>
@@ -6666,7 +6736,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>202503464</v>
+        <v>202511047</v>
       </c>
       <c r="B332" t="n">
         <v>559660</v>
@@ -6674,7 +6744,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>202206636</v>
+        <v>202205022</v>
       </c>
       <c r="B333" t="n">
         <v>559660</v>
@@ -6682,7 +6752,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>202007851</v>
+        <v>202512130</v>
       </c>
       <c r="B334" t="n">
         <v>559660</v>
@@ -6690,7 +6760,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>202205318</v>
+        <v>202204883</v>
       </c>
       <c r="B335" t="n">
         <v>559660</v>
@@ -6698,7 +6768,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>202502510</v>
+        <v>202108673</v>
       </c>
       <c r="B336" t="n">
         <v>559660</v>
@@ -6706,7 +6776,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>202511047</v>
+        <v>202207871</v>
       </c>
       <c r="B337" t="n">
         <v>559660</v>
@@ -6714,7 +6784,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>202205022</v>
+        <v>202208726</v>
       </c>
       <c r="B338" t="n">
         <v>559660</v>
@@ -6722,7 +6792,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>202512130</v>
+        <v>202511257</v>
       </c>
       <c r="B339" t="n">
         <v>559660</v>
@@ -6730,7 +6800,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>202204883</v>
+        <v>202108877</v>
       </c>
       <c r="B340" t="n">
         <v>559660</v>
@@ -6738,7 +6808,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>202108673</v>
+        <v>202204802</v>
       </c>
       <c r="B341" t="n">
         <v>559660</v>
@@ -6746,7 +6816,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>202207871</v>
+        <v>202211070</v>
       </c>
       <c r="B342" t="n">
         <v>559660</v>
@@ -6754,7 +6824,7 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>202208726</v>
+        <v>202514197</v>
       </c>
       <c r="B343" t="n">
         <v>559660</v>
@@ -6762,7 +6832,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>202511257</v>
+        <v>202510623</v>
       </c>
       <c r="B344" t="n">
         <v>559660</v>
@@ -6770,7 +6840,7 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>202108877</v>
+        <v>202502513</v>
       </c>
       <c r="B345" t="n">
         <v>559660</v>
@@ -6778,7 +6848,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>202204802</v>
+        <v>202206180</v>
       </c>
       <c r="B346" t="n">
         <v>559660</v>
@@ -6786,7 +6856,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>202211070</v>
+        <v>202208957</v>
       </c>
       <c r="B347" t="n">
         <v>559660</v>
@@ -6794,7 +6864,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>202514197</v>
+        <v>202512262</v>
       </c>
       <c r="B348" t="n">
         <v>559660</v>
@@ -6802,7 +6872,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>202510623</v>
+        <v>202510624</v>
       </c>
       <c r="B349" t="n">
         <v>559660</v>
@@ -6810,7 +6880,7 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>202502513</v>
+        <v>202108751</v>
       </c>
       <c r="B350" t="n">
         <v>559660</v>
@@ -6818,7 +6888,7 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>202206180</v>
+        <v>202500548</v>
       </c>
       <c r="B351" t="n">
         <v>559660</v>
@@ -6826,47 +6896,47 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>202208957</v>
+        <v>202502507</v>
       </c>
       <c r="B352" t="n">
-        <v>559660</v>
+        <v>559659</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>202512262</v>
+        <v>202500539</v>
       </c>
       <c r="B353" t="n">
-        <v>559660</v>
+        <v>559659</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>202510624</v>
+        <v>202108685</v>
       </c>
       <c r="B354" t="n">
-        <v>559660</v>
+        <v>559659</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>202108751</v>
+        <v>202510620</v>
       </c>
       <c r="B355" t="n">
-        <v>559660</v>
+        <v>559659</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>202500548</v>
+        <v>202503496</v>
       </c>
       <c r="B356" t="n">
-        <v>559660</v>
+        <v>559659</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>202502507</v>
+        <v>202206097</v>
       </c>
       <c r="B357" t="n">
         <v>559659</v>
@@ -6874,7 +6944,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>202500539</v>
+        <v>202206173</v>
       </c>
       <c r="B358" t="n">
         <v>559659</v>
@@ -6882,7 +6952,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>202108685</v>
+        <v>202500541</v>
       </c>
       <c r="B359" t="n">
         <v>559659</v>
@@ -6890,7 +6960,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>202510620</v>
+        <v>202500542</v>
       </c>
       <c r="B360" t="n">
         <v>559659</v>
@@ -6898,7 +6968,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>202503496</v>
+        <v>202205629</v>
       </c>
       <c r="B361" t="n">
         <v>559659</v>
@@ -6906,7 +6976,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>202206097</v>
+        <v>202210537</v>
       </c>
       <c r="B362" t="n">
         <v>559659</v>
@@ -6914,7 +6984,7 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>202206173</v>
+        <v>202510622</v>
       </c>
       <c r="B363" t="n">
         <v>559659</v>
@@ -6922,7 +6992,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>202500541</v>
+        <v>202502508</v>
       </c>
       <c r="B364" t="n">
         <v>559659</v>
@@ -6930,7 +7000,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>202500542</v>
+        <v>202102359</v>
       </c>
       <c r="B365" t="n">
         <v>559659</v>
@@ -6938,7 +7008,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>202205629</v>
+        <v>202511053</v>
       </c>
       <c r="B366" t="n">
         <v>559659</v>
@@ -6946,7 +7016,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>202210537</v>
+        <v>202503416</v>
       </c>
       <c r="B367" t="n">
         <v>559659</v>
@@ -6954,7 +7024,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>202510622</v>
+        <v>202503464</v>
       </c>
       <c r="B368" t="n">
         <v>559659</v>
@@ -6962,7 +7032,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>202502508</v>
+        <v>202206636</v>
       </c>
       <c r="B369" t="n">
         <v>559659</v>
@@ -6970,7 +7040,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>202102359</v>
+        <v>202205318</v>
       </c>
       <c r="B370" t="n">
         <v>559659</v>
@@ -6978,7 +7048,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>202511053</v>
+        <v>202502510</v>
       </c>
       <c r="B371" t="n">
         <v>559659</v>
@@ -6986,7 +7056,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>202503416</v>
+        <v>202511047</v>
       </c>
       <c r="B372" t="n">
         <v>559659</v>
@@ -6994,7 +7064,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>202503464</v>
+        <v>202205022</v>
       </c>
       <c r="B373" t="n">
         <v>559659</v>
@@ -7002,7 +7072,7 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>202206636</v>
+        <v>202512130</v>
       </c>
       <c r="B374" t="n">
         <v>559659</v>
@@ -7010,7 +7080,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>202205318</v>
+        <v>202204883</v>
       </c>
       <c r="B375" t="n">
         <v>559659</v>
@@ -7018,7 +7088,7 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>202502510</v>
+        <v>202108673</v>
       </c>
       <c r="B376" t="n">
         <v>559659</v>
@@ -7026,7 +7096,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>202511047</v>
+        <v>202207871</v>
       </c>
       <c r="B377" t="n">
         <v>559659</v>
@@ -7034,7 +7104,7 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>202205022</v>
+        <v>201902398</v>
       </c>
       <c r="B378" t="n">
         <v>559659</v>
@@ -7042,7 +7112,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>202512130</v>
+        <v>202208726</v>
       </c>
       <c r="B379" t="n">
         <v>559659</v>
@@ -7050,7 +7120,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>202204883</v>
+        <v>202511257</v>
       </c>
       <c r="B380" t="n">
         <v>559659</v>
@@ -7058,7 +7128,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>202108673</v>
+        <v>202108877</v>
       </c>
       <c r="B381" t="n">
         <v>559659</v>
@@ -7066,7 +7136,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>202207871</v>
+        <v>202409902</v>
       </c>
       <c r="B382" t="n">
         <v>559659</v>
@@ -7074,7 +7144,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>201902398</v>
+        <v>202204802</v>
       </c>
       <c r="B383" t="n">
         <v>559659</v>
@@ -7082,7 +7152,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>202208726</v>
+        <v>202211070</v>
       </c>
       <c r="B384" t="n">
         <v>559659</v>
@@ -7090,7 +7160,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>202511257</v>
+        <v>202514197</v>
       </c>
       <c r="B385" t="n">
         <v>559659</v>
@@ -7098,7 +7168,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>202108877</v>
+        <v>202510623</v>
       </c>
       <c r="B386" t="n">
         <v>559659</v>
@@ -7106,7 +7176,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>202409902</v>
+        <v>202502513</v>
       </c>
       <c r="B387" t="n">
         <v>559659</v>
@@ -7114,7 +7184,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>202204802</v>
+        <v>201906293</v>
       </c>
       <c r="B388" t="n">
         <v>559659</v>
@@ -7122,7 +7192,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>202211070</v>
+        <v>202206180</v>
       </c>
       <c r="B389" t="n">
         <v>559659</v>
@@ -7130,7 +7200,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>202514197</v>
+        <v>202208957</v>
       </c>
       <c r="B390" t="n">
         <v>559659</v>
@@ -7138,7 +7208,7 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>202510623</v>
+        <v>202108751</v>
       </c>
       <c r="B391" t="n">
         <v>559659</v>
@@ -7146,7 +7216,7 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>202502513</v>
+        <v>202512468</v>
       </c>
       <c r="B392" t="n">
         <v>559659</v>
@@ -7154,7 +7224,7 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>201906293</v>
+        <v>202503018</v>
       </c>
       <c r="B393" t="n">
         <v>559659</v>
@@ -7162,7 +7232,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>202206180</v>
+        <v>202409904</v>
       </c>
       <c r="B394" t="n">
         <v>559659</v>
@@ -7170,7 +7240,7 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>202208957</v>
+        <v>202500548</v>
       </c>
       <c r="B395" t="n">
         <v>559659</v>
@@ -7178,47 +7248,47 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>202108751</v>
+        <v>202502507</v>
       </c>
       <c r="B396" t="n">
-        <v>559659</v>
+        <v>559658</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>202512468</v>
+        <v>202500539</v>
       </c>
       <c r="B397" t="n">
-        <v>559659</v>
+        <v>559658</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>202503018</v>
+        <v>202108685</v>
       </c>
       <c r="B398" t="n">
-        <v>559659</v>
+        <v>559658</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>202409904</v>
+        <v>202100684</v>
       </c>
       <c r="B399" t="n">
-        <v>559659</v>
+        <v>559658</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>202500548</v>
+        <v>202510620</v>
       </c>
       <c r="B400" t="n">
-        <v>559659</v>
+        <v>559658</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>202502507</v>
+        <v>202503496</v>
       </c>
       <c r="B401" t="n">
         <v>559658</v>
@@ -7226,7 +7296,7 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>202500539</v>
+        <v>202206097</v>
       </c>
       <c r="B402" t="n">
         <v>559658</v>
@@ -7234,7 +7304,7 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>202108685</v>
+        <v>200907258</v>
       </c>
       <c r="B403" t="n">
         <v>559658</v>
@@ -7242,7 +7312,7 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>202100684</v>
+        <v>202109244</v>
       </c>
       <c r="B404" t="n">
         <v>559658</v>
@@ -7250,7 +7320,7 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>202510620</v>
+        <v>202206173</v>
       </c>
       <c r="B405" t="n">
         <v>559658</v>
@@ -7258,7 +7328,7 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>202503496</v>
+        <v>202500541</v>
       </c>
       <c r="B406" t="n">
         <v>559658</v>
@@ -7266,7 +7336,7 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>202206097</v>
+        <v>202500542</v>
       </c>
       <c r="B407" t="n">
         <v>559658</v>
@@ -7274,7 +7344,7 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>200907258</v>
+        <v>202205629</v>
       </c>
       <c r="B408" t="n">
         <v>559658</v>
@@ -7282,7 +7352,7 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>202109244</v>
+        <v>202210537</v>
       </c>
       <c r="B409" t="n">
         <v>559658</v>
@@ -7290,7 +7360,7 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>202206173</v>
+        <v>202510622</v>
       </c>
       <c r="B410" t="n">
         <v>559658</v>
@@ -7298,7 +7368,7 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>202500541</v>
+        <v>202502508</v>
       </c>
       <c r="B411" t="n">
         <v>559658</v>
@@ -7306,7 +7376,7 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>202500542</v>
+        <v>202102359</v>
       </c>
       <c r="B412" t="n">
         <v>559658</v>
@@ -7314,7 +7384,7 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>202205629</v>
+        <v>202500543</v>
       </c>
       <c r="B413" t="n">
         <v>559658</v>
@@ -7322,7 +7392,7 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>202210537</v>
+        <v>202511053</v>
       </c>
       <c r="B414" t="n">
         <v>559658</v>
@@ -7330,7 +7400,7 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>202510622</v>
+        <v>202508617</v>
       </c>
       <c r="B415" t="n">
         <v>559658</v>
@@ -7338,7 +7408,7 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>202502508</v>
+        <v>202503416</v>
       </c>
       <c r="B416" t="n">
         <v>559658</v>
@@ -7346,7 +7416,7 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>202102359</v>
+        <v>202503464</v>
       </c>
       <c r="B417" t="n">
         <v>559658</v>
@@ -7354,7 +7424,7 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>202500543</v>
+        <v>202206636</v>
       </c>
       <c r="B418" t="n">
         <v>559658</v>
@@ -7362,7 +7432,7 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>202511053</v>
+        <v>202205318</v>
       </c>
       <c r="B419" t="n">
         <v>559658</v>
@@ -7370,7 +7440,7 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>202508617</v>
+        <v>202500544</v>
       </c>
       <c r="B420" t="n">
         <v>559658</v>
@@ -7378,7 +7448,7 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>202503416</v>
+        <v>202502510</v>
       </c>
       <c r="B421" t="n">
         <v>559658</v>
@@ -7386,7 +7456,7 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>202503464</v>
+        <v>202205022</v>
       </c>
       <c r="B422" t="n">
         <v>559658</v>
@@ -7394,7 +7464,7 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>202206636</v>
+        <v>202204883</v>
       </c>
       <c r="B423" t="n">
         <v>559658</v>
@@ -7402,7 +7472,7 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>202205318</v>
+        <v>202108673</v>
       </c>
       <c r="B424" t="n">
         <v>559658</v>
@@ -7410,7 +7480,7 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>202500544</v>
+        <v>202207871</v>
       </c>
       <c r="B425" t="n">
         <v>559658</v>
@@ -7418,7 +7488,7 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>202502510</v>
+        <v>202208726</v>
       </c>
       <c r="B426" t="n">
         <v>559658</v>
@@ -7426,7 +7496,7 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>202205022</v>
+        <v>202511257</v>
       </c>
       <c r="B427" t="n">
         <v>559658</v>
@@ -7434,7 +7504,7 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>202204883</v>
+        <v>202108877</v>
       </c>
       <c r="B428" t="n">
         <v>559658</v>
@@ -7442,7 +7512,7 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>202108673</v>
+        <v>202500545</v>
       </c>
       <c r="B429" t="n">
         <v>559658</v>
@@ -7450,7 +7520,7 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>202207871</v>
+        <v>202204802</v>
       </c>
       <c r="B430" t="n">
         <v>559658</v>
@@ -7458,7 +7528,7 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>202208726</v>
+        <v>201606434</v>
       </c>
       <c r="B431" t="n">
         <v>559658</v>
@@ -7466,7 +7536,7 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>202511257</v>
+        <v>202008219</v>
       </c>
       <c r="B432" t="n">
         <v>559658</v>
@@ -7474,7 +7544,7 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>202108877</v>
+        <v>202510623</v>
       </c>
       <c r="B433" t="n">
         <v>559658</v>
@@ -7482,7 +7552,7 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>202500545</v>
+        <v>201906293</v>
       </c>
       <c r="B434" t="n">
         <v>559658</v>
@@ -7490,7 +7560,7 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>202204802</v>
+        <v>202206180</v>
       </c>
       <c r="B435" t="n">
         <v>559658</v>
@@ -7498,7 +7568,7 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>201606434</v>
+        <v>202502654</v>
       </c>
       <c r="B436" t="n">
         <v>559658</v>
@@ -7506,7 +7576,7 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>202008219</v>
+        <v>202208957</v>
       </c>
       <c r="B437" t="n">
         <v>559658</v>
@@ -7514,7 +7584,7 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>202510623</v>
+        <v>202108751</v>
       </c>
       <c r="B438" t="n">
         <v>559658</v>
@@ -7522,7 +7592,7 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>201906293</v>
+        <v>202500548</v>
       </c>
       <c r="B439" t="n">
         <v>559658</v>
@@ -7530,7 +7600,7 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>202206180</v>
+        <v>202508615</v>
       </c>
       <c r="B440" t="n">
         <v>559658</v>
@@ -7538,415 +7608,415 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>202502654</v>
+        <v>202502507</v>
       </c>
       <c r="B441" t="n">
-        <v>559658</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>202208957</v>
+        <v>202500539</v>
       </c>
       <c r="B442" t="n">
-        <v>559658</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>202108751</v>
+        <v>202208028</v>
       </c>
       <c r="B443" t="n">
-        <v>559658</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>202500548</v>
+        <v>202108685</v>
       </c>
       <c r="B444" t="n">
-        <v>559658</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>202508615</v>
+        <v>202100684</v>
       </c>
       <c r="B445" t="n">
-        <v>559658</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>202502842</v>
+        <v>202109775</v>
       </c>
       <c r="B446" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>202502507</v>
+        <v>202510620</v>
       </c>
       <c r="B447" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>202500539</v>
+        <v>202503496</v>
       </c>
       <c r="B448" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>202502639</v>
+        <v>202206097</v>
       </c>
       <c r="B449" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>202108685</v>
+        <v>202510621</v>
       </c>
       <c r="B450" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>202100684</v>
+        <v>200907258</v>
       </c>
       <c r="B451" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>202109775</v>
+        <v>202107100</v>
       </c>
       <c r="B452" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>202510620</v>
+        <v>202206173</v>
       </c>
       <c r="B453" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>202503496</v>
+        <v>202500541</v>
       </c>
       <c r="B454" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>202206097</v>
+        <v>202500542</v>
       </c>
       <c r="B455" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>202109244</v>
+        <v>202205629</v>
       </c>
       <c r="B456" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>202206173</v>
+        <v>202210537</v>
       </c>
       <c r="B457" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>202500541</v>
+        <v>202510622</v>
       </c>
       <c r="B458" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>202500542</v>
+        <v>202502508</v>
       </c>
       <c r="B459" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>202205629</v>
+        <v>202502841</v>
       </c>
       <c r="B460" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>202210537</v>
+        <v>202102359</v>
       </c>
       <c r="B461" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>202510622</v>
+        <v>202500543</v>
       </c>
       <c r="B462" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>202502508</v>
+        <v>202511053</v>
       </c>
       <c r="B463" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>202102359</v>
+        <v>202503416</v>
       </c>
       <c r="B464" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>201908253</v>
+        <v>202206636</v>
       </c>
       <c r="B465" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>202511053</v>
+        <v>202007851</v>
       </c>
       <c r="B466" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>202503416</v>
+        <v>202205318</v>
       </c>
       <c r="B467" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>202503464</v>
+        <v>202500544</v>
       </c>
       <c r="B468" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>202206636</v>
+        <v>202502510</v>
       </c>
       <c r="B469" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>202205318</v>
+        <v>202205022</v>
       </c>
       <c r="B470" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>202500544</v>
+        <v>202204883</v>
       </c>
       <c r="B471" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>202502510</v>
+        <v>202108673</v>
       </c>
       <c r="B472" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>202205022</v>
+        <v>202207871</v>
       </c>
       <c r="B473" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>202108777</v>
+        <v>202508437</v>
       </c>
       <c r="B474" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>202204883</v>
+        <v>202208726</v>
       </c>
       <c r="B475" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>202108673</v>
+        <v>202511257</v>
       </c>
       <c r="B476" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>202207871</v>
+        <v>202108877</v>
       </c>
       <c r="B477" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>202208726</v>
+        <v>202500545</v>
       </c>
       <c r="B478" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>202511257</v>
+        <v>202204802</v>
       </c>
       <c r="B479" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>202108877</v>
+        <v>202211070</v>
       </c>
       <c r="B480" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>202500545</v>
+        <v>201606434</v>
       </c>
       <c r="B481" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>202409902</v>
+        <v>202008219</v>
       </c>
       <c r="B482" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>202204802</v>
+        <v>202501687</v>
       </c>
       <c r="B483" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>202211070</v>
+        <v>202502849</v>
       </c>
       <c r="B484" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>201606434</v>
+        <v>202510623</v>
       </c>
       <c r="B485" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>202510623</v>
+        <v>202206180</v>
       </c>
       <c r="B486" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>202401558</v>
+        <v>202502654</v>
       </c>
       <c r="B487" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>202206180</v>
+        <v>202208957</v>
       </c>
       <c r="B488" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>202208957</v>
+        <v>202510624</v>
       </c>
       <c r="B489" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>202510624</v>
+        <v>202108751</v>
       </c>
       <c r="B490" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>202108751</v>
+        <v>202500548</v>
       </c>
       <c r="B491" t="n">
-        <v>559656</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>202409904</v>
+        <v>202502842</v>
       </c>
       <c r="B492" t="n">
         <v>559656</v>
@@ -7954,7 +8024,7 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>202500548</v>
+        <v>202502507</v>
       </c>
       <c r="B493" t="n">
         <v>559656</v>
@@ -7962,7 +8032,7 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>202402696</v>
+        <v>202500539</v>
       </c>
       <c r="B494" t="n">
         <v>559656</v>
@@ -7970,7 +8040,7 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>202502844</v>
+        <v>202502639</v>
       </c>
       <c r="B495" t="n">
         <v>559656</v>
@@ -7978,375 +8048,375 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>202502507</v>
+        <v>202108685</v>
       </c>
       <c r="B496" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>202500539</v>
+        <v>202100684</v>
       </c>
       <c r="B497" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>202502639</v>
+        <v>202109775</v>
       </c>
       <c r="B498" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>202108685</v>
+        <v>202510620</v>
       </c>
       <c r="B499" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>202100684</v>
+        <v>202503496</v>
       </c>
       <c r="B500" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>202510620</v>
+        <v>202206097</v>
       </c>
       <c r="B501" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>202503496</v>
+        <v>202109244</v>
       </c>
       <c r="B502" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>202206097</v>
+        <v>202206173</v>
       </c>
       <c r="B503" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>202510621</v>
+        <v>202500541</v>
       </c>
       <c r="B504" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>200907258</v>
+        <v>202500542</v>
       </c>
       <c r="B505" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>202206173</v>
+        <v>202205629</v>
       </c>
       <c r="B506" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>202500541</v>
+        <v>202210537</v>
       </c>
       <c r="B507" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>202500542</v>
+        <v>202510622</v>
       </c>
       <c r="B508" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>202205629</v>
+        <v>202502508</v>
       </c>
       <c r="B509" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>202210537</v>
+        <v>202102359</v>
       </c>
       <c r="B510" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>202510622</v>
+        <v>201908253</v>
       </c>
       <c r="B511" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>202502508</v>
+        <v>202511053</v>
       </c>
       <c r="B512" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>202502841</v>
+        <v>202503416</v>
       </c>
       <c r="B513" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>202102359</v>
+        <v>202503464</v>
       </c>
       <c r="B514" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>201908253</v>
+        <v>202206636</v>
       </c>
       <c r="B515" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>202511053</v>
+        <v>202205318</v>
       </c>
       <c r="B516" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>202508617</v>
+        <v>202500544</v>
       </c>
       <c r="B517" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>202503416</v>
+        <v>202502510</v>
       </c>
       <c r="B518" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>202503464</v>
+        <v>202205022</v>
       </c>
       <c r="B519" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>202206636</v>
+        <v>202108777</v>
       </c>
       <c r="B520" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>202007851</v>
+        <v>202204883</v>
       </c>
       <c r="B521" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>202205318</v>
+        <v>202108673</v>
       </c>
       <c r="B522" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>202500544</v>
+        <v>202207871</v>
       </c>
       <c r="B523" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>202502510</v>
+        <v>202208726</v>
       </c>
       <c r="B524" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>202205022</v>
+        <v>202511257</v>
       </c>
       <c r="B525" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>202204883</v>
+        <v>202108877</v>
       </c>
       <c r="B526" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>202108673</v>
+        <v>202500545</v>
       </c>
       <c r="B527" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>202207871</v>
+        <v>202409902</v>
       </c>
       <c r="B528" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>202208726</v>
+        <v>202204802</v>
       </c>
       <c r="B529" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>202511257</v>
+        <v>202211070</v>
       </c>
       <c r="B530" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>202108877</v>
+        <v>201606434</v>
       </c>
       <c r="B531" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>202500545</v>
+        <v>202510623</v>
       </c>
       <c r="B532" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>202409902</v>
+        <v>202401558</v>
       </c>
       <c r="B533" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>202204802</v>
+        <v>202206180</v>
       </c>
       <c r="B534" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>201606434</v>
+        <v>202208957</v>
       </c>
       <c r="B535" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>202008219</v>
+        <v>202510624</v>
       </c>
       <c r="B536" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>202510623</v>
+        <v>202108751</v>
       </c>
       <c r="B537" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>202401558</v>
+        <v>202409904</v>
       </c>
       <c r="B538" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>202206180</v>
+        <v>202500548</v>
       </c>
       <c r="B539" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>202208957</v>
+        <v>202402696</v>
       </c>
       <c r="B540" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>202108751</v>
+        <v>202502844</v>
       </c>
       <c r="B541" t="n">
-        <v>559655</v>
+        <v>559656</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>202409904</v>
+        <v>202502507</v>
       </c>
       <c r="B542" t="n">
         <v>559655</v>
@@ -8354,7 +8424,7 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>202500548</v>
+        <v>202500539</v>
       </c>
       <c r="B543" t="n">
         <v>559655</v>
@@ -8362,7 +8432,7 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>202508615</v>
+        <v>202502639</v>
       </c>
       <c r="B544" t="n">
         <v>559655</v>
@@ -8370,154 +8440,154 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>202502506</v>
+        <v>202108685</v>
       </c>
       <c r="B545" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>202502507</v>
+        <v>202100684</v>
       </c>
       <c r="B546" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>202500539</v>
+        <v>202510620</v>
       </c>
       <c r="B547" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>202108685</v>
+        <v>202503496</v>
       </c>
       <c r="B548" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>202100684</v>
+        <v>202206097</v>
       </c>
       <c r="B549" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>202510620</v>
+        <v>202510621</v>
       </c>
       <c r="B550" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>202503496</v>
+        <v>200907258</v>
       </c>
       <c r="B551" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>202206097</v>
+        <v>202206173</v>
       </c>
       <c r="B552" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>202510621</v>
+        <v>202500541</v>
       </c>
       <c r="B553" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>202206173</v>
+        <v>202500542</v>
       </c>
       <c r="B554" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>202500541</v>
+        <v>202205629</v>
       </c>
       <c r="B555" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>202500542</v>
+        <v>202210537</v>
       </c>
       <c r="B556" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>202205629</v>
+        <v>202510622</v>
       </c>
       <c r="B557" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>202210537</v>
+        <v>202502508</v>
       </c>
       <c r="B558" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>202510622</v>
+        <v>202502841</v>
       </c>
       <c r="B559" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>202502508</v>
+        <v>202102359</v>
       </c>
       <c r="B560" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>202102359</v>
+        <v>201908253</v>
       </c>
       <c r="B561" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>202500543</v>
+        <v>202511053</v>
       </c>
       <c r="B562" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>202511053</v>
+        <v>202508617</v>
       </c>
       <c r="B563" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="564">
@@ -8525,7 +8595,7 @@
         <v>202503416</v>
       </c>
       <c r="B564" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="565">
@@ -8533,7 +8603,7 @@
         <v>202503464</v>
       </c>
       <c r="B565" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="566">
@@ -8541,7 +8611,7 @@
         <v>202206636</v>
       </c>
       <c r="B566" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="567">
@@ -8549,7 +8619,7 @@
         <v>202007851</v>
       </c>
       <c r="B567" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="568">
@@ -8557,7 +8627,7 @@
         <v>202205318</v>
       </c>
       <c r="B568" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="569">
@@ -8565,7 +8635,7 @@
         <v>202500544</v>
       </c>
       <c r="B569" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="570">
@@ -8573,7 +8643,7 @@
         <v>202502510</v>
       </c>
       <c r="B570" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="571">
@@ -8581,7 +8651,7 @@
         <v>202205022</v>
       </c>
       <c r="B571" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="572">
@@ -8589,7 +8659,7 @@
         <v>202204883</v>
       </c>
       <c r="B572" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="573">
@@ -8597,7 +8667,7 @@
         <v>202108673</v>
       </c>
       <c r="B573" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="574">
@@ -8605,7 +8675,7 @@
         <v>202207871</v>
       </c>
       <c r="B574" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="575">
@@ -8613,7 +8683,7 @@
         <v>202208726</v>
       </c>
       <c r="B575" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="576">
@@ -8621,7 +8691,7 @@
         <v>202511257</v>
       </c>
       <c r="B576" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="577">
@@ -8629,7 +8699,7 @@
         <v>202108877</v>
       </c>
       <c r="B577" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="578">
@@ -8637,7 +8707,7 @@
         <v>202500545</v>
       </c>
       <c r="B578" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="579">
@@ -8645,7 +8715,7 @@
         <v>202409902</v>
       </c>
       <c r="B579" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="580">
@@ -8653,23 +8723,23 @@
         <v>202204802</v>
       </c>
       <c r="B580" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>202211070</v>
+        <v>201606434</v>
       </c>
       <c r="B581" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>201606434</v>
+        <v>202008219</v>
       </c>
       <c r="B582" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="583">
@@ -8677,7 +8747,7 @@
         <v>202510623</v>
       </c>
       <c r="B583" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="584">
@@ -8685,7 +8755,7 @@
         <v>202401558</v>
       </c>
       <c r="B584" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="585">
@@ -8693,7 +8763,7 @@
         <v>202206180</v>
       </c>
       <c r="B585" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="586">
@@ -8701,39 +8771,39 @@
         <v>202208957</v>
       </c>
       <c r="B586" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>202510624</v>
+        <v>202108751</v>
       </c>
       <c r="B587" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>202108751</v>
+        <v>202409904</v>
       </c>
       <c r="B588" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>202409904</v>
+        <v>202500548</v>
       </c>
       <c r="B589" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>202500548</v>
+        <v>202508615</v>
       </c>
       <c r="B590" t="n">
-        <v>559654</v>
+        <v>559655</v>
       </c>
     </row>
   </sheetData>
